--- a/finance/_refresh_careem.xlsx
+++ b/finance/_refresh_careem.xlsx
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2380,7 +2380,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2574,7 +2574,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -2962,7 +2962,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3156,7 +3156,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3350,7 +3350,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3544,7 +3544,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3738,7 +3738,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4126,7 +4126,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4320,7 +4320,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4514,7 +4514,7 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J16,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J16,1))</f>
         <v/>
       </c>
       <c r="L16" s="34">
@@ -4708,7 +4708,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -4902,7 +4902,7 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J18,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J18,1))</f>
         <v/>
       </c>
       <c r="L18" s="34">
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5290,7 +5290,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5484,7 +5484,7 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J21,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J21,1))</f>
         <v/>
       </c>
       <c r="L21" s="34">
@@ -5678,7 +5678,7 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J22,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
         <v/>
       </c>
       <c r="L22" s="34">
@@ -5872,7 +5872,7 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J23,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J23,1))</f>
         <v/>
       </c>
       <c r="L23" s="34">
@@ -6066,7 +6066,7 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J24,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J24,1))</f>
         <v/>
       </c>
       <c r="L24" s="34">
@@ -6260,7 +6260,7 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J25,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J25,1))</f>
         <v/>
       </c>
       <c r="L25" s="34">
@@ -6454,7 +6454,7 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J26,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J26,1))</f>
         <v/>
       </c>
       <c r="L26" s="34">
@@ -6648,7 +6648,7 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J27,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J27,1))</f>
         <v/>
       </c>
       <c r="L27" s="34">
@@ -6842,7 +6842,7 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J28,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J28,1))</f>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -7036,7 +7036,7 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J29,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J29,1))</f>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -7220,7 +7220,7 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J30,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J30,1))</f>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -7386,7 +7386,7 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J31,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J31,1))</f>
         <v/>
       </c>
       <c r="L31" s="34">
@@ -7562,7 +7562,7 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J32,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J32,1))</f>
         <v/>
       </c>
       <c r="L32" s="34">
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -7950,7 +7950,7 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J34,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J34,1))</f>
         <v/>
       </c>
       <c r="L34" s="34">
@@ -8144,7 +8144,7 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J35,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J35,1))</f>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -8328,7 +8328,7 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J36,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J36,1))</f>
         <v/>
       </c>
       <c r="L36" s="34">
@@ -8494,7 +8494,7 @@
         <v/>
       </c>
       <c r="K37" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J37,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
         <v/>
       </c>
       <c r="L37" s="34">
@@ -8670,7 +8670,7 @@
         <v/>
       </c>
       <c r="K38" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J38,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J38,1))</f>
         <v/>
       </c>
       <c r="L38" s="34">
@@ -8864,7 +8864,7 @@
         <v/>
       </c>
       <c r="K39" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J39,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
         <v/>
       </c>
       <c r="L39" s="34">

--- a/finance/_refresh_careem.xlsx
+++ b/finance/_refresh_careem.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_careem.xlsx
+++ b/finance/_refresh_careem.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$45</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$45</definedName>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -780,84 +780,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -874,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1363,11 +1422,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1376,7 +1435,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1386,29 +1445,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1416,29 +1471,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1446,255 +1497,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1724,7 +1823,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1850,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1766,7 +1865,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1839,10 +1938,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2003,7 +2102,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2013,12 +2112,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_careem.xlsx
+++ b/finance/_refresh_careem.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$45</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$45</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$57</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -188,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -324,6 +324,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1913,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1958,14 +1964,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2202,40 +2209,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2393,7 +2405,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2401,7 +2413,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2409,27 +2421,32 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="inlineStr">
+      <c r="AX4" s="44" t="inlineStr">
         <is>
           <t>Palm ultra-lux cluster (One&amp;Only&lt;-&gt;Zabeel Saray). Road-served. T5/low.</t>
         </is>
       </c>
-      <c r="AX4" s="44" t="inlineStr">
+      <c r="AY4" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -2587,7 +2604,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2595,7 +2612,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2603,27 +2620,32 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="inlineStr">
+      <c r="AX5" s="44" t="inlineStr">
         <is>
           <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Bluewaters/Ain Dubai is a genuine water-served island attraction adjacent to Dubai Marina.</t>
         </is>
       </c>
-      <c r="AX5" s="44" t="inlineStr">
+      <c r="AY5" s="44" t="inlineStr">
         <is>
           <t>RTA marine = 18.4M riders 2025 (WAM, T1); bulk are ~1km Creek abras (R3-ABRA, different micro-corridor). Premium non-abra modes a small fraction.</t>
         </is>
@@ -2781,7 +2803,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2789,7 +2811,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2797,27 +2819,32 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="inlineStr">
+      <c r="AX6" s="44" t="inlineStr">
         <is>
           <t>Palm resort cluster (Kempinski&lt;-&gt;Atlantis). Road-served. T5/low.</t>
         </is>
       </c>
-      <c r="AX6" s="44" t="inlineStr">
+      <c r="AY6" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -2975,7 +3002,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2983,7 +3010,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2991,27 +3018,32 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="inlineStr">
+      <c r="AX7" s="44" t="inlineStr">
         <is>
           <t>Urban Dubai beach-club leisure hop. Road-served. T5/low.</t>
         </is>
       </c>
-      <c r="AX7" s="44" t="inlineStr">
+      <c r="AY7" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -3169,7 +3201,7 @@
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3177,7 +3209,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3185,27 +3217,32 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="inlineStr">
+      <c r="AX8" s="44" t="inlineStr">
         <is>
           <t>Atlantis The Palm (1,544 rooms) road-served; premium marine arrival opportunity-to-create. T5/low.</t>
         </is>
       </c>
-      <c r="AX8" s="44" t="inlineStr">
+      <c r="AY8" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
         </is>
@@ -3363,7 +3400,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3371,7 +3408,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3379,27 +3416,32 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="n"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n"/>
-      <c r="AT9" s="43">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n"/>
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="inlineStr">
+      <c r="AX9" s="44" t="inlineStr">
         <is>
           <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Creek Marina&lt;-&gt;Al Seef is an operating RTA marine corridor.</t>
         </is>
       </c>
-      <c r="AX9" s="44" t="inlineStr">
+      <c r="AY9" s="44" t="inlineStr">
         <is>
           <t>18.4M RTA marine is ~all sub-1km abras (R3-ABRA); premium water-taxi/ferry tier is a small fraction.</t>
         </is>
@@ -3557,7 +3599,7 @@
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3565,7 +3607,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3573,27 +3615,32 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
-      <c r="AT10" s="43">
+      <c r="AS10" s="41" t="n"/>
+      <c r="AT10" s="42" t="n"/>
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="inlineStr">
+      <c r="AX10" s="44" t="inlineStr">
         <is>
           <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Dubai Marina (Mina Seyahi) premium resort hop.</t>
         </is>
       </c>
-      <c r="AX10" s="44" t="inlineStr">
+      <c r="AY10" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -3751,7 +3798,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3759,7 +3806,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3767,27 +3814,32 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="inlineStr">
+      <c r="AX11" s="44" t="inlineStr">
         <is>
           <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Lulu Island - boat-only undeveloped island fronting the Corniche.</t>
         </is>
       </c>
-      <c r="AX11" s="44" t="inlineStr">
+      <c r="AY11" s="44" t="inlineStr">
         <is>
           <t>Lulu boat-only (R3-EXCEPTION) but undeveloped/limited-access -&gt; small day-visit pool.</t>
         </is>
@@ -3945,7 +3997,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3953,7 +4005,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3961,27 +4013,32 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR12" s="41" t="n"/>
-      <c r="AS12" s="42" t="n"/>
-      <c r="AT12" s="43">
+      <c r="AS12" s="41" t="n"/>
+      <c r="AT12" s="42" t="n"/>
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="inlineStr">
+      <c r="AX12" s="44" t="inlineStr">
         <is>
           <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Palm Jumeirah served by RTA Water Taxi + Dubai Ferry.</t>
         </is>
       </c>
-      <c r="AX12" s="44" t="inlineStr">
+      <c r="AY12" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -4139,7 +4196,7 @@
         <v/>
       </c>
       <c r="AL13" s="34">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),FLOOR(AK13/R13,1)))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
         <v/>
       </c>
       <c r="AM13" s="38">
@@ -4147,7 +4204,7 @@
         <v/>
       </c>
       <c r="AN13" s="36">
-        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AS13="",9.9E+99,AS13),AK13/R13))</f>
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
         <v/>
       </c>
       <c r="AO13" s="38">
@@ -4155,27 +4212,32 @@
         <v/>
       </c>
       <c r="AP13" s="40" t="n"/>
-      <c r="AQ13" s="41" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR13" s="41" t="n"/>
-      <c r="AS13" s="42" t="n"/>
-      <c r="AT13" s="43">
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="42" t="n"/>
+      <c r="AU13" s="43">
         <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AU13" s="43">
+      <c r="AV13" s="43">
         <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AV13" s="43">
+      <c r="AW13" s="43">
         <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
         <v/>
       </c>
-      <c r="AW13" s="44" t="inlineStr">
+      <c r="AX13" s="44" t="inlineStr">
         <is>
           <t>Emirates Palace (flagship AD luxury hotel) marina arrival; road-served; opportunity-to-create. T5/low.</t>
         </is>
       </c>
-      <c r="AX13" s="44" t="inlineStr">
+      <c r="AY13" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -4333,7 +4395,7 @@
         <v/>
       </c>
       <c r="AL14" s="34">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),FLOOR(AK14/R14,1)))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
         <v/>
       </c>
       <c r="AM14" s="38">
@@ -4341,7 +4403,7 @@
         <v/>
       </c>
       <c r="AN14" s="36">
-        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AS14="",9.9E+99,AS14),AK14/R14))</f>
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
         <v/>
       </c>
       <c r="AO14" s="38">
@@ -4349,27 +4411,32 @@
         <v/>
       </c>
       <c r="AP14" s="40" t="n"/>
-      <c r="AQ14" s="41" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR14" s="41" t="n"/>
-      <c r="AS14" s="42" t="n"/>
-      <c r="AT14" s="43">
+      <c r="AS14" s="41" t="n"/>
+      <c r="AT14" s="42" t="n"/>
+      <c r="AU14" s="43">
         <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AU14" s="43">
+      <c r="AV14" s="43">
         <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AV14" s="43">
+      <c r="AW14" s="43">
         <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
         <v/>
       </c>
-      <c r="AW14" s="44" t="inlineStr">
+      <c r="AX14" s="44" t="inlineStr">
         <is>
           <t>Intra-The-World offshore hop; both boat-only. Greenfield premium per-seat. T5/low.</t>
         </is>
       </c>
-      <c r="AX14" s="44" t="inlineStr">
+      <c r="AY14" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -4388,18 +4455,18 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Marina Mall / Breakwater Marina → Al Bateen Marina</t>
+          <t>Bulgari Yacht Club &amp; Marina → La Mer / J1 Beach Jetty</t>
         </is>
       </c>
       <c r="D15" s="31" t="n">
         <v>2.6</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
@@ -4507,7 +4574,7 @@
         <v/>
       </c>
       <c r="AG15" s="31" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
@@ -4527,7 +4594,7 @@
         <v/>
       </c>
       <c r="AL15" s="34">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),FLOOR(AK15/R15,1)))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
         <v/>
       </c>
       <c r="AM15" s="38">
@@ -4535,7 +4602,7 @@
         <v/>
       </c>
       <c r="AN15" s="36">
-        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AS15="",9.9E+99,AS15),AK15/R15))</f>
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
         <v/>
       </c>
       <c r="AO15" s="38">
@@ -4543,27 +4610,32 @@
         <v/>
       </c>
       <c r="AP15" s="40" t="n"/>
-      <c r="AQ15" s="41" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR15" s="41" t="n"/>
-      <c r="AS15" s="42" t="n"/>
-      <c r="AT15" s="43">
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="42" t="n"/>
+      <c r="AU15" s="43">
         <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AU15" s="43">
+      <c r="AV15" s="43">
         <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AV15" s="43">
+      <c r="AW15" s="43">
         <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
         <v/>
       </c>
-      <c r="AW15" s="44" t="inlineStr">
-        <is>
-          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Al Bateen Marina, AD.</t>
-        </is>
-      </c>
       <c r="AX15" s="44" t="inlineStr">
+        <is>
+          <t>Urban Dubai beach-club leisure hop (Bulgari Bay&lt;-&gt;La Mer/J1). Road-served. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY15" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -4582,18 +4654,18 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Bulgari Yacht Club &amp; Marina → La Mer / J1 Beach Jetty</t>
+          <t>Marina Mall / Breakwater Marina → Al Bateen Marina</t>
         </is>
       </c>
       <c r="D16" s="31" t="n">
         <v>2.6</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G16" s="32" t="inlineStr">
@@ -4701,7 +4773,7 @@
         <v/>
       </c>
       <c r="AG16" s="31" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="AH16" s="32" t="inlineStr">
         <is>
@@ -4721,7 +4793,7 @@
         <v/>
       </c>
       <c r="AL16" s="34">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),FLOOR(AK16/R16,1)))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),FLOOR(AK16/R16,1)))</f>
         <v/>
       </c>
       <c r="AM16" s="38">
@@ -4729,7 +4801,7 @@
         <v/>
       </c>
       <c r="AN16" s="36">
-        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AS16="",9.9E+99,AS16),AK16/R16))</f>
+        <f>IF(OR(AG16="",R16=0),"",MIN(IF(AT16="",9.9E+99,AT16),AK16/R16))</f>
         <v/>
       </c>
       <c r="AO16" s="38">
@@ -4737,27 +4809,32 @@
         <v/>
       </c>
       <c r="AP16" s="40" t="n"/>
-      <c r="AQ16" s="41" t="n"/>
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR16" s="41" t="n"/>
-      <c r="AS16" s="42" t="n"/>
-      <c r="AT16" s="43">
+      <c r="AS16" s="41" t="n"/>
+      <c r="AT16" s="42" t="n"/>
+      <c r="AU16" s="43">
         <f>IF(((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_thin*ROUND(K16*L16*revleg_thin,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_thin,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AU16" s="43">
+      <c r="AV16" s="43">
         <f>IF(((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_mid*ROUND(K16*L16*revleg_mid,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_mid,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AV16" s="43">
+      <c r="AW16" s="43">
         <f>IF(((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16))&lt;=0,"",VLOOKUP(B16,country_opex,7,FALSE)/((S16*pax_cap*load_full*ROUND(K16*L16*revleg_full,0))-(((battery/range_nm)*D16*ROUND(K16*L16*revleg_full,0)*VLOOKUP(B16,country_opex,3,FALSE))+V16+W16+X16+Y16+Z16)))</f>
         <v/>
       </c>
-      <c r="AW16" s="44" t="inlineStr">
-        <is>
-          <t>Urban Dubai beach-club leisure hop (Bulgari Bay&lt;-&gt;La Mer/J1). Road-served. T5/low.</t>
-        </is>
-      </c>
       <c r="AX16" s="44" t="inlineStr">
+        <is>
+          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Al Bateen Marina, AD.</t>
+        </is>
+      </c>
+      <c r="AY16" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -4776,25 +4853,15 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>Al Bateen Marina → Hudayriat Marina</t>
+          <t>Dubai Harbour Marina → Anantara The Palm Dubai Jetty</t>
         </is>
       </c>
       <c r="D17" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>90</v>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="G17" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
       <c r="H17" s="19" t="n">
         <v>1</v>
       </c>
@@ -4894,19 +4961,9 @@
         <f>((D17*O17/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D17*O17*VLOOKUP(B17,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG17" s="31" t="n">
-        <v>35000</v>
-      </c>
-      <c r="AH17" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI17" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG17" s="31" t="n"/>
+      <c r="AH17" s="32" t="n"/>
+      <c r="AI17" s="32" t="n"/>
       <c r="AJ17" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -4915,7 +4972,7 @@
         <v/>
       </c>
       <c r="AL17" s="34">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),FLOOR(AK17/R17,1)))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),FLOOR(AK17/R17,1)))</f>
         <v/>
       </c>
       <c r="AM17" s="38">
@@ -4923,7 +4980,7 @@
         <v/>
       </c>
       <c r="AN17" s="36">
-        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AS17="",9.9E+99,AS17),AK17/R17))</f>
+        <f>IF(OR(AG17="",R17=0),"",MIN(IF(AT17="",9.9E+99,AT17),AK17/R17))</f>
         <v/>
       </c>
       <c r="AO17" s="38">
@@ -4931,31 +4988,28 @@
         <v/>
       </c>
       <c r="AP17" s="40" t="n"/>
-      <c r="AQ17" s="41" t="n"/>
+      <c r="AQ17" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR17" s="41" t="n"/>
-      <c r="AS17" s="42" t="n"/>
-      <c r="AT17" s="43">
+      <c r="AS17" s="41" t="n"/>
+      <c r="AT17" s="42" t="n"/>
+      <c r="AU17" s="43">
         <f>IF(((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_thin*ROUND(K17*L17*revleg_thin,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_thin,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AU17" s="43">
+      <c r="AV17" s="43">
         <f>IF(((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_mid*ROUND(K17*L17*revleg_mid,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_mid,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AV17" s="43">
+      <c r="AW17" s="43">
         <f>IF(((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17))&lt;=0,"",VLOOKUP(B17,country_opex,7,FALSE)/((S17*pax_cap*load_full*ROUND(K17*L17*revleg_full,0))-(((battery/range_nm)*D17*ROUND(K17*L17*revleg_full,0)*VLOOKUP(B17,country_opex,3,FALSE))+V17+W17+X17+Y17+Z17)))</f>
         <v/>
       </c>
-      <c r="AW17" s="44" t="inlineStr">
-        <is>
-          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Hudayriat Island leisure/beach destination, AD.</t>
-        </is>
-      </c>
-      <c r="AX17" s="44" t="inlineStr">
-        <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
-        </is>
-      </c>
+      <c r="AX17" s="44" t="n"/>
+      <c r="AY17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
@@ -4970,18 +5024,18 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>Côte d'Azur Resort Marina (Heart of Europe) → Bulgari Yacht Club &amp; Marina</t>
+          <t>Al Bateen Marina → Hudayriat Marina</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G18" s="32" t="inlineStr">
@@ -5089,7 +5143,7 @@
         <v/>
       </c>
       <c r="AG18" s="31" t="n">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
@@ -5109,7 +5163,7 @@
         <v/>
       </c>
       <c r="AL18" s="34">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),FLOOR(AK18/R18,1)))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),FLOOR(AK18/R18,1)))</f>
         <v/>
       </c>
       <c r="AM18" s="38">
@@ -5117,7 +5171,7 @@
         <v/>
       </c>
       <c r="AN18" s="36">
-        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AS18="",9.9E+99,AS18),AK18/R18))</f>
+        <f>IF(OR(AG18="",R18=0),"",MIN(IF(AT18="",9.9E+99,AT18),AK18/R18))</f>
         <v/>
       </c>
       <c r="AO18" s="38">
@@ -5125,27 +5179,32 @@
         <v/>
       </c>
       <c r="AP18" s="40" t="n"/>
-      <c r="AQ18" s="41" t="n"/>
+      <c r="AQ18" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR18" s="41" t="n"/>
-      <c r="AS18" s="42" t="n"/>
-      <c r="AT18" s="43">
+      <c r="AS18" s="41" t="n"/>
+      <c r="AT18" s="42" t="n"/>
+      <c r="AU18" s="43">
         <f>IF(((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_thin*ROUND(K18*L18*revleg_thin,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_thin,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AU18" s="43">
+      <c r="AV18" s="43">
         <f>IF(((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_mid*ROUND(K18*L18*revleg_mid,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_mid,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AV18" s="43">
+      <c r="AW18" s="43">
         <f>IF(((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18))&lt;=0,"",VLOOKUP(B18,country_opex,7,FALSE)/((S18*pax_cap*load_full*ROUND(K18*L18*revleg_full,0))-(((battery/range_nm)*D18*ROUND(K18*L18*revleg_full,0)*VLOOKUP(B18,country_opex,3,FALSE))+V18+W18+X18+Y18+Z18)))</f>
         <v/>
       </c>
-      <c r="AW18" s="44" t="inlineStr">
-        <is>
-          <t>The World (boat-only)&lt;-&gt;Bulgari (Jumeirah Bay) luxury hop. Greenfield. T5/low.</t>
-        </is>
-      </c>
       <c r="AX18" s="44" t="inlineStr">
+        <is>
+          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Hudayriat Island leisure/beach destination, AD.</t>
+        </is>
+      </c>
+      <c r="AY18" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
@@ -5164,23 +5223,23 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>Saadiyat Beach Club Jetty → Zaya Nurai Island Jetty</t>
+          <t>Côte d'Azur Resort Marina (Heart of Europe) → Bulgari Yacht Club &amp; Marina</t>
         </is>
       </c>
       <c r="D19" s="31" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="E19" s="26" t="n">
         <v>150</v>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H19" s="19" t="n">
@@ -5283,11 +5342,11 @@
         <v/>
       </c>
       <c r="AG19" s="31" t="n">
-        <v>45000</v>
+        <v>20000</v>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
@@ -5303,7 +5362,7 @@
         <v/>
       </c>
       <c r="AL19" s="34">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),FLOOR(AK19/R19,1)))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),FLOOR(AK19/R19,1)))</f>
         <v/>
       </c>
       <c r="AM19" s="38">
@@ -5311,7 +5370,7 @@
         <v/>
       </c>
       <c r="AN19" s="36">
-        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AS19="",9.9E+99,AS19),AK19/R19))</f>
+        <f>IF(OR(AG19="",R19=0),"",MIN(IF(AT19="",9.9E+99,AT19),AK19/R19))</f>
         <v/>
       </c>
       <c r="AO19" s="38">
@@ -5319,29 +5378,34 @@
         <v/>
       </c>
       <c r="AP19" s="40" t="n"/>
-      <c r="AQ19" s="41" t="n"/>
+      <c r="AQ19" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR19" s="41" t="n"/>
-      <c r="AS19" s="42" t="n"/>
-      <c r="AT19" s="43">
+      <c r="AS19" s="41" t="n"/>
+      <c r="AT19" s="42" t="n"/>
+      <c r="AU19" s="43">
         <f>IF(((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_thin*ROUND(K19*L19*revleg_thin,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_thin,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AU19" s="43">
+      <c r="AV19" s="43">
         <f>IF(((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_mid*ROUND(K19*L19*revleg_mid,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_mid,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AV19" s="43">
+      <c r="AW19" s="43">
         <f>IF(((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19))&lt;=0,"",VLOOKUP(B19,country_opex,7,FALSE)/((S19*pax_cap*load_full*ROUND(K19*L19*revleg_full,0))-(((battery/range_nm)*D19*ROUND(K19*L19*revleg_full,0)*VLOOKUP(B19,country_opex,3,FALSE))+V19+W19+X19+Y19+Z19)))</f>
         <v/>
       </c>
-      <c r="AW19" s="44" t="inlineStr">
-        <is>
-          <t>Saadiyat Beach Club-&gt;Zaya Nurai Island (4.4nm). WATER-ONLY (12-15min boat from Saadiyat; boat-only, 32 villas + 23 residences). Day-pass + transfer redemption ladder; premium per-seat $150.</t>
-        </is>
-      </c>
       <c r="AX19" s="44" t="inlineStr">
         <is>
-          <t>Boat-only -&gt; FULLY addressable (R3-EXCEPTION). 32 villas + 23 residences stay-pool + day-club guests (major Saadiyat day-trip).</t>
+          <t>The World (boat-only)&lt;-&gt;Bulgari (Jumeirah Bay) luxury hop. Greenfield. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY19" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
       </c>
     </row>
@@ -5358,23 +5422,23 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Atlantis The Royal Jetty</t>
+          <t>Saadiyat Beach Club Jetty → Zaya Nurai Island Jetty</t>
         </is>
       </c>
       <c r="D20" s="31" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="G20" s="32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>med</t>
         </is>
       </c>
       <c r="H20" s="19" t="n">
@@ -5477,7 +5541,7 @@
         <v/>
       </c>
       <c r="AG20" s="31" t="n">
-        <v>10000</v>
+        <v>45000</v>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
@@ -5497,7 +5561,7 @@
         <v/>
       </c>
       <c r="AL20" s="34">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),FLOOR(AK20/R20,1)))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),FLOOR(AK20/R20,1)))</f>
         <v/>
       </c>
       <c r="AM20" s="38">
@@ -5505,7 +5569,7 @@
         <v/>
       </c>
       <c r="AN20" s="36">
-        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AS20="",9.9E+99,AS20),AK20/R20))</f>
+        <f>IF(OR(AG20="",R20=0),"",MIN(IF(AT20="",9.9E+99,AT20),AK20/R20))</f>
         <v/>
       </c>
       <c r="AO20" s="38">
@@ -5513,29 +5577,34 @@
         <v/>
       </c>
       <c r="AP20" s="40" t="n"/>
-      <c r="AQ20" s="41" t="n"/>
+      <c r="AQ20" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR20" s="41" t="n"/>
-      <c r="AS20" s="42" t="n"/>
-      <c r="AT20" s="43">
+      <c r="AS20" s="41" t="n"/>
+      <c r="AT20" s="42" t="n"/>
+      <c r="AU20" s="43">
         <f>IF(((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_thin*ROUND(K20*L20*revleg_thin,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_thin,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AU20" s="43">
+      <c r="AV20" s="43">
         <f>IF(((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_mid*ROUND(K20*L20*revleg_mid,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_mid,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AV20" s="43">
+      <c r="AW20" s="43">
         <f>IF(((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20))&lt;=0,"",VLOOKUP(B20,country_opex,7,FALSE)/((S20*pax_cap*load_full*ROUND(K20*L20*revleg_full,0))-(((battery/range_nm)*D20*ROUND(K20*L20*revleg_full,0)*VLOOKUP(B20,country_opex,3,FALSE))+V20+W20+X20+Y20+Z20)))</f>
         <v/>
       </c>
-      <c r="AW20" s="44" t="inlineStr">
-        <is>
-          <t>Atlantis The Royal (795 keys) road-served; signature marine arrival opportunity-to-create. T5/low.</t>
-        </is>
-      </c>
       <c r="AX20" s="44" t="inlineStr">
         <is>
-          <t>OPT-IN luxury-arrival fraction only (R3-LAND road-served). 795 keys x occ -&gt; small opt-in marine pool.</t>
+          <t>Saadiyat Beach Club-&gt;Zaya Nurai Island (4.4nm). WATER-ONLY (12-15min boat from Saadiyat; boat-only, 32 villas + 23 residences). Day-pass + transfer redemption ladder; premium per-seat $150.</t>
+        </is>
+      </c>
+      <c r="AY20" s="44" t="inlineStr">
+        <is>
+          <t>Boat-only -&gt; FULLY addressable (R3-EXCEPTION). 32 villas + 23 residences stay-pool + day-club guests (major Saadiyat day-trip).</t>
         </is>
       </c>
     </row>
@@ -5552,14 +5621,14 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>Jebel Dhanna / Ruwais Ferry Terminal → Sir Bani Yas Cruise Port</t>
+          <t>Dubai Harbour Marina → Atlantis The Royal Jetty</t>
         </is>
       </c>
       <c r="D21" s="31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
@@ -5671,7 +5740,7 @@
         <v/>
       </c>
       <c r="AG21" s="31" t="n">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
@@ -5691,7 +5760,7 @@
         <v/>
       </c>
       <c r="AL21" s="34">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),FLOOR(AK21/R21,1)))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),FLOOR(AK21/R21,1)))</f>
         <v/>
       </c>
       <c r="AM21" s="38">
@@ -5699,7 +5768,7 @@
         <v/>
       </c>
       <c r="AN21" s="36">
-        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AS21="",9.9E+99,AS21),AK21/R21))</f>
+        <f>IF(OR(AG21="",R21=0),"",MIN(IF(AT21="",9.9E+99,AT21),AK21/R21))</f>
         <v/>
       </c>
       <c r="AO21" s="38">
@@ -5707,29 +5776,34 @@
         <v/>
       </c>
       <c r="AP21" s="40" t="n"/>
-      <c r="AQ21" s="41" t="n"/>
+      <c r="AQ21" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR21" s="41" t="n"/>
-      <c r="AS21" s="42" t="n"/>
-      <c r="AT21" s="43">
+      <c r="AS21" s="41" t="n"/>
+      <c r="AT21" s="42" t="n"/>
+      <c r="AU21" s="43">
         <f>IF(((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_thin*ROUND(K21*L21*revleg_thin,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_thin,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AU21" s="43">
+      <c r="AV21" s="43">
         <f>IF(((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_mid*ROUND(K21*L21*revleg_mid,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_mid,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AV21" s="43">
+      <c r="AW21" s="43">
         <f>IF(((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21))&lt;=0,"",VLOOKUP(B21,country_opex,7,FALSE)/((S21*pax_cap*load_full*ROUND(K21*L21*revleg_full,0))-(((battery/range_nm)*D21*ROUND(K21*L21*revleg_full,0)*VLOOKUP(B21,country_opex,3,FALSE))+V21+W21+X21+Y21+Z21)))</f>
         <v/>
       </c>
-      <c r="AW21" s="44" t="inlineStr">
-        <is>
-          <t>Sir Bani Yas boat-only (~8km offshore). 3 Anantara resorts ~124 keys. Guest boat transfer FREE today (R-UAE-1) -&gt; $90 opportunity-to-create / day-guest analog. T5/low.</t>
-        </is>
-      </c>
       <c r="AX21" s="44" t="inlineStr">
         <is>
-          <t>Sir Bani Yas boat-only (R3-EXCEPTION). 3 Anantara resorts ~124 keys + Arabian Wildlife Park day-visitors via Jebel Dhanna ferry.</t>
+          <t>Atlantis The Royal (795 keys) road-served; signature marine arrival opportunity-to-create. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY21" s="44" t="inlineStr">
+        <is>
+          <t>OPT-IN luxury-arrival fraction only (R3-LAND road-served). 795 keys x occ -&gt; small opt-in marine pool.</t>
         </is>
       </c>
     </row>
@@ -5746,14 +5820,14 @@
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Burj Al Arab Private Jetty</t>
+          <t>Jebel Dhanna / Ruwais Ferry Terminal → Sir Bani Yas Cruise Port</t>
         </is>
       </c>
       <c r="D22" s="31" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
@@ -5865,7 +5939,7 @@
         <v/>
       </c>
       <c r="AG22" s="31" t="n">
-        <v>5000</v>
+        <v>60000</v>
       </c>
       <c r="AH22" s="32" t="inlineStr">
         <is>
@@ -5885,7 +5959,7 @@
         <v/>
       </c>
       <c r="AL22" s="34">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),FLOOR(AK22/R22,1)))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),FLOOR(AK22/R22,1)))</f>
         <v/>
       </c>
       <c r="AM22" s="38">
@@ -5893,7 +5967,7 @@
         <v/>
       </c>
       <c r="AN22" s="36">
-        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AS22="",9.9E+99,AS22),AK22/R22))</f>
+        <f>IF(OR(AG22="",R22=0),"",MIN(IF(AT22="",9.9E+99,AT22),AK22/R22))</f>
         <v/>
       </c>
       <c r="AO22" s="38">
@@ -5901,29 +5975,34 @@
         <v/>
       </c>
       <c r="AP22" s="40" t="n"/>
-      <c r="AQ22" s="41" t="n"/>
+      <c r="AQ22" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR22" s="41" t="n"/>
-      <c r="AS22" s="42" t="n"/>
-      <c r="AT22" s="43">
+      <c r="AS22" s="41" t="n"/>
+      <c r="AT22" s="42" t="n"/>
+      <c r="AU22" s="43">
         <f>IF(((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_thin*ROUND(K22*L22*revleg_thin,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_thin,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AU22" s="43">
+      <c r="AV22" s="43">
         <f>IF(((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_mid*ROUND(K22*L22*revleg_mid,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_mid,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AV22" s="43">
+      <c r="AW22" s="43">
         <f>IF(((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22))&lt;=0,"",VLOOKUP(B22,country_opex,7,FALSE)/((S22*pax_cap*load_full*ROUND(K22*L22*revleg_full,0))-(((battery/range_nm)*D22*ROUND(K22*L22*revleg_full,0)*VLOOKUP(B22,country_opex,3,FALSE))+V22+W22+X22+Y22+Z22)))</f>
         <v/>
       </c>
-      <c r="AW22" s="44" t="inlineStr">
-        <is>
-          <t>Burj Al Arab (202 suites) road-served; iconic signature marine arrival. T5/low.</t>
-        </is>
-      </c>
       <c r="AX22" s="44" t="inlineStr">
         <is>
-          <t>OPT-IN only (R3-LAND). 202 suites x occ -&gt; modest base + experiential day-guest yacht-arrivals.</t>
+          <t>Sir Bani Yas boat-only (~8km offshore). 3 Anantara resorts ~124 keys. Guest boat transfer FREE today (R-UAE-1) -&gt; $90 opportunity-to-create / day-guest analog. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY22" s="44" t="inlineStr">
+        <is>
+          <t>Sir Bani Yas boat-only (R3-EXCEPTION). 3 Anantara resorts ~124 keys + Arabian Wildlife Park day-visitors via Jebel Dhanna ferry.</t>
         </is>
       </c>
     </row>
@@ -5940,18 +6019,18 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Marina Mall / Breakwater Marina → Reem Island Marina (Najmat / Marina Square)</t>
+          <t>Dubai Harbour Marina → Burj Al Arab Private Jetty</t>
         </is>
       </c>
       <c r="D23" s="31" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G23" s="32" t="inlineStr">
@@ -6059,11 +6138,11 @@
         <v/>
       </c>
       <c r="AG23" s="31" t="n">
-        <v>35000</v>
+        <v>5000</v>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
@@ -6079,7 +6158,7 @@
         <v/>
       </c>
       <c r="AL23" s="34">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),FLOOR(AK23/R23,1)))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),FLOOR(AK23/R23,1)))</f>
         <v/>
       </c>
       <c r="AM23" s="38">
@@ -6087,7 +6166,7 @@
         <v/>
       </c>
       <c r="AN23" s="36">
-        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AS23="",9.9E+99,AS23),AK23/R23))</f>
+        <f>IF(OR(AG23="",R23=0),"",MIN(IF(AT23="",9.9E+99,AT23),AK23/R23))</f>
         <v/>
       </c>
       <c r="AO23" s="38">
@@ -6095,29 +6174,34 @@
         <v/>
       </c>
       <c r="AP23" s="40" t="n"/>
-      <c r="AQ23" s="41" t="n"/>
+      <c r="AQ23" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR23" s="41" t="n"/>
-      <c r="AS23" s="42" t="n"/>
-      <c r="AT23" s="43">
+      <c r="AS23" s="41" t="n"/>
+      <c r="AT23" s="42" t="n"/>
+      <c r="AU23" s="43">
         <f>IF(((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_thin*ROUND(K23*L23*revleg_thin,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_thin,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AU23" s="43">
+      <c r="AV23" s="43">
         <f>IF(((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_mid*ROUND(K23*L23*revleg_mid,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_mid,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AV23" s="43">
+      <c r="AW23" s="43">
         <f>IF(((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23))&lt;=0,"",VLOOKUP(B23,country_opex,7,FALSE)/((S23*pax_cap*load_full*ROUND(K23*L23*revleg_full,0))-(((battery/range_nm)*D23*ROUND(K23*L23*revleg_full,0)*VLOOKUP(B23,country_opex,3,FALSE))+V23+W23+X23+Y23+Z23)))</f>
         <v/>
       </c>
-      <c r="AW23" s="44" t="inlineStr">
-        <is>
-          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Reem Island (Najmat/Marina Square).</t>
-        </is>
-      </c>
       <c r="AX23" s="44" t="inlineStr">
         <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
+          <t>Burj Al Arab (202 suites) road-served; iconic signature marine arrival. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY23" s="44" t="inlineStr">
+        <is>
+          <t>OPT-IN only (R3-LAND). 202 suites x occ -&gt; modest base + experiential day-guest yacht-arrivals.</t>
         </is>
       </c>
     </row>
@@ -6134,14 +6218,14 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Anantara World Islands Resort Jetty (planned)</t>
+          <t>Marina Mall / Breakwater Marina → Reem Island Marina (Najmat / Marina Square)</t>
         </is>
       </c>
       <c r="D24" s="31" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
@@ -6253,11 +6337,11 @@
         <v/>
       </c>
       <c r="AG24" s="31" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
@@ -6273,7 +6357,7 @@
         <v/>
       </c>
       <c r="AL24" s="34">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),FLOOR(AK24/R24,1)))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),FLOOR(AK24/R24,1)))</f>
         <v/>
       </c>
       <c r="AM24" s="38">
@@ -6281,7 +6365,7 @@
         <v/>
       </c>
       <c r="AN24" s="36">
-        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AS24="",9.9E+99,AS24),AK24/R24))</f>
+        <f>IF(OR(AG24="",R24=0),"",MIN(IF(AT24="",9.9E+99,AT24),AK24/R24))</f>
         <v/>
       </c>
       <c r="AO24" s="38">
@@ -6289,29 +6373,34 @@
         <v/>
       </c>
       <c r="AP24" s="40" t="n"/>
-      <c r="AQ24" s="41" t="n"/>
+      <c r="AQ24" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR24" s="41" t="n"/>
-      <c r="AS24" s="42" t="n"/>
-      <c r="AT24" s="43">
+      <c r="AS24" s="41" t="n"/>
+      <c r="AT24" s="42" t="n"/>
+      <c r="AU24" s="43">
         <f>IF(((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_thin*ROUND(K24*L24*revleg_thin,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_thin,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AU24" s="43">
+      <c r="AV24" s="43">
         <f>IF(((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_mid*ROUND(K24*L24*revleg_mid,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_mid,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AV24" s="43">
+      <c r="AW24" s="43">
         <f>IF(((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24))&lt;=0,"",VLOOKUP(B24,country_opex,7,FALSE)/((S24*pax_cap*load_full*ROUND(K24*L24*revleg_full,0))-(((battery/range_nm)*D24*ROUND(K24*L24*revleg_full,0)*VLOOKUP(B24,country_opex,3,FALSE))+V24+W24+X24+Y24+Z24)))</f>
         <v/>
       </c>
-      <c r="AW24" s="44" t="inlineStr">
-        <is>
-          <t>Anantara World Islands Resort (boat-only; Forbes/Expedia 'accessible only by boat'). Resort shuttle ~AED 150/pax RETURN (~$20/way); premium per-seat modeled $80.</t>
-        </is>
-      </c>
       <c r="AX24" s="44" t="inlineStr">
         <is>
-          <t>Boot-only -&gt; arrivals=crossing ridership FULLY addressable (R3-EXCEPTION). ~70 keys x ~65% occ + day-guests.</t>
+          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. Reem Island (Najmat/Marina Square).</t>
+        </is>
+      </c>
+      <c r="AY24" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
       </c>
     </row>
@@ -6328,14 +6417,14 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>Saadiyat Beach Club Jetty → Marina Mall / Breakwater Marina</t>
+          <t>Dubai Harbour Marina → Anantara World Islands Resort Jetty (planned)</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
@@ -6447,11 +6536,11 @@
         <v/>
       </c>
       <c r="AG25" s="31" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
@@ -6467,7 +6556,7 @@
         <v/>
       </c>
       <c r="AL25" s="34">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),FLOOR(AK25/R25,1)))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),FLOOR(AK25/R25,1)))</f>
         <v/>
       </c>
       <c r="AM25" s="38">
@@ -6475,7 +6564,7 @@
         <v/>
       </c>
       <c r="AN25" s="36">
-        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AS25="",9.9E+99,AS25),AK25/R25))</f>
+        <f>IF(OR(AG25="",R25=0),"",MIN(IF(AT25="",9.9E+99,AT25),AK25/R25))</f>
         <v/>
       </c>
       <c r="AO25" s="38">
@@ -6483,29 +6572,34 @@
         <v/>
       </c>
       <c r="AP25" s="40" t="n"/>
-      <c r="AQ25" s="41" t="n"/>
+      <c r="AQ25" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR25" s="41" t="n"/>
-      <c r="AS25" s="42" t="n"/>
-      <c r="AT25" s="43">
+      <c r="AS25" s="41" t="n"/>
+      <c r="AT25" s="42" t="n"/>
+      <c r="AU25" s="43">
         <f>IF(((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_thin*ROUND(K25*L25*revleg_thin,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_thin,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AU25" s="43">
+      <c r="AV25" s="43">
         <f>IF(((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_mid*ROUND(K25*L25*revleg_mid,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_mid,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AV25" s="43">
+      <c r="AW25" s="43">
         <f>IF(((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25))&lt;=0,"",VLOOKUP(B25,country_opex,7,FALSE)/((S25*pax_cap*load_full*ROUND(K25*L25*revleg_full,0))-(((battery/range_nm)*D25*ROUND(K25*L25*revleg_full,0)*VLOOKUP(B25,country_opex,3,FALSE))+V25+W25+X25+Y25+Z25)))</f>
         <v/>
       </c>
-      <c r="AW25" s="44" t="inlineStr">
-        <is>
-          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. AD Corniche&lt;-&gt;Saadiyat marine hop.</t>
-        </is>
-      </c>
       <c r="AX25" s="44" t="inlineStr">
         <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
+          <t>Anantara World Islands Resort (boat-only; Forbes/Expedia 'accessible only by boat'). Resort shuttle ~AED 150/pax RETURN (~$20/way); premium per-seat modeled $80.</t>
+        </is>
+      </c>
+      <c r="AY25" s="44" t="inlineStr">
+        <is>
+          <t>Boot-only -&gt; arrivals=crossing ridership FULLY addressable (R3-EXCEPTION). ~70 keys x ~65% occ + day-guests.</t>
         </is>
       </c>
     </row>
@@ -6522,18 +6616,18 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Côte d'Azur Resort Marina (Heart of Europe)</t>
+          <t>Saadiyat Beach Club Jetty → Marina Mall / Breakwater Marina</t>
         </is>
       </c>
       <c r="D26" s="31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G26" s="32" t="inlineStr">
@@ -6641,16 +6735,16 @@
         <v/>
       </c>
       <c r="AG26" s="31" t="n">
-        <v>70000</v>
+        <v>25000</v>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AJ26" s="39" t="n">
@@ -6661,7 +6755,7 @@
         <v/>
       </c>
       <c r="AL26" s="34">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),FLOOR(AK26/R26,1)))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),FLOOR(AK26/R26,1)))</f>
         <v/>
       </c>
       <c r="AM26" s="38">
@@ -6669,7 +6763,7 @@
         <v/>
       </c>
       <c r="AN26" s="36">
-        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AS26="",9.9E+99,AS26),AK26/R26))</f>
+        <f>IF(OR(AG26="",R26=0),"",MIN(IF(AT26="",9.9E+99,AT26),AK26/R26))</f>
         <v/>
       </c>
       <c r="AO26" s="38">
@@ -6677,29 +6771,34 @@
         <v/>
       </c>
       <c r="AP26" s="40" t="n"/>
-      <c r="AQ26" s="41" t="n"/>
+      <c r="AQ26" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR26" s="41" t="n"/>
-      <c r="AS26" s="42" t="n"/>
-      <c r="AT26" s="43">
+      <c r="AS26" s="41" t="n"/>
+      <c r="AT26" s="42" t="n"/>
+      <c r="AU26" s="43">
         <f>IF(((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_thin*ROUND(K26*L26*revleg_thin,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_thin,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AU26" s="43">
+      <c r="AV26" s="43">
         <f>IF(((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_mid*ROUND(K26*L26*revleg_mid,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_mid,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AV26" s="43">
+      <c r="AW26" s="43">
         <f>IF(((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26))&lt;=0,"",VLOOKUP(B26,country_opex,7,FALSE)/((S26*pax_cap*load_full*ROUND(K26*L26*revleg_full,0))-(((battery/range_nm)*D26*ROUND(K26*L26*revleg_full,0)*VLOOKUP(B26,country_opex,3,FALSE))+V26+W26+X26+Y26+Z26)))</f>
         <v/>
       </c>
-      <c r="AW26" s="44" t="inlineStr">
-        <is>
-          <t>The World (Heart of Europe/Cote d'Azur) boat-only offshore. Shared per-seat $56-120/pax; resort transfers bundled. T5/low - opportunity-to-create.</t>
-        </is>
-      </c>
       <c r="AX26" s="44" t="inlineStr">
         <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
+          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. AD Corniche&lt;-&gt;Saadiyat marine hop.</t>
+        </is>
+      </c>
+      <c r="AY26" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
       </c>
     </row>
@@ -6716,11 +6815,11 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>Bluewaters Marina → Heart of Europe — Main Marina (The World)</t>
+          <t>Dubai Harbour Marina → Côte d'Azur Resort Marina (Heart of Europe)</t>
         </is>
       </c>
       <c r="D27" s="31" t="n">
-        <v>9.880000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>175</v>
@@ -6835,16 +6934,16 @@
         <v/>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AJ27" s="39" t="n">
@@ -6855,7 +6954,7 @@
         <v/>
       </c>
       <c r="AL27" s="34">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),FLOOR(AK27/R27,1)))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),FLOOR(AK27/R27,1)))</f>
         <v/>
       </c>
       <c r="AM27" s="38">
@@ -6863,7 +6962,7 @@
         <v/>
       </c>
       <c r="AN27" s="36">
-        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AS27="",9.9E+99,AS27),AK27/R27))</f>
+        <f>IF(OR(AG27="",R27=0),"",MIN(IF(AT27="",9.9E+99,AT27),AK27/R27))</f>
         <v/>
       </c>
       <c r="AO27" s="38">
@@ -6871,29 +6970,34 @@
         <v/>
       </c>
       <c r="AP27" s="40" t="n"/>
-      <c r="AQ27" s="41" t="n"/>
+      <c r="AQ27" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR27" s="41" t="n"/>
-      <c r="AS27" s="42" t="n"/>
-      <c r="AT27" s="43">
+      <c r="AS27" s="41" t="n"/>
+      <c r="AT27" s="42" t="n"/>
+      <c r="AU27" s="43">
         <f>IF(((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_thin*ROUND(K27*L27*revleg_thin,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_thin,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AU27" s="43">
+      <c r="AV27" s="43">
         <f>IF(((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_mid*ROUND(K27*L27*revleg_mid,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_mid,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AV27" s="43">
+      <c r="AW27" s="43">
         <f>IF(((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27))&lt;=0,"",VLOOKUP(B27,country_opex,7,FALSE)/((S27*pax_cap*load_full*ROUND(K27*L27*revleg_full,0))-(((battery/range_nm)*D27*ROUND(K27*L27*revleg_full,0)*VLOOKUP(B27,country_opex,3,FALSE))+V27+W27+X27+Y27+Z27)))</f>
         <v/>
       </c>
-      <c r="AW27" s="44" t="inlineStr">
-        <is>
-          <t>The World (Heart of Europe) boat-only offshore; greenfield. T5/low.</t>
-        </is>
-      </c>
       <c r="AX27" s="44" t="inlineStr">
         <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
+          <t>The World (Heart of Europe/Cote d'Azur) boat-only offshore. Shared per-seat $56-120/pax; resort transfers bundled. T5/low - opportunity-to-create.</t>
+        </is>
+      </c>
+      <c r="AY27" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
         </is>
       </c>
     </row>
@@ -6910,25 +7014,15 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Bulgari Yacht Club &amp; Marina</t>
+          <t>Vida Beach Resort Umm Al Quwain → Sharjah Waterfront City marina</t>
         </is>
       </c>
       <c r="D28" s="31" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E28" s="26" t="n">
-        <v>200</v>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G28" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="32" t="n"/>
       <c r="H28" s="19" t="n">
         <v>1</v>
       </c>
@@ -7028,19 +7122,9 @@
         <f>((D28*O28/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D28*O28*VLOOKUP(B28,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG28" s="31" t="n">
-        <v>4000</v>
-      </c>
-      <c r="AH28" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="AI28" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG28" s="31" t="n"/>
+      <c r="AH28" s="32" t="n"/>
+      <c r="AI28" s="32" t="n"/>
       <c r="AJ28" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -7049,7 +7133,7 @@
         <v/>
       </c>
       <c r="AL28" s="34">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),FLOOR(AK28/R28,1)))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),FLOOR(AK28/R28,1)))</f>
         <v/>
       </c>
       <c r="AM28" s="38">
@@ -7057,7 +7141,7 @@
         <v/>
       </c>
       <c r="AN28" s="36">
-        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AS28="",9.9E+99,AS28),AK28/R28))</f>
+        <f>IF(OR(AG28="",R28=0),"",MIN(IF(AT28="",9.9E+99,AT28),AK28/R28))</f>
         <v/>
       </c>
       <c r="AO28" s="38">
@@ -7065,31 +7149,28 @@
         <v/>
       </c>
       <c r="AP28" s="40" t="n"/>
-      <c r="AQ28" s="41" t="n"/>
+      <c r="AQ28" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR28" s="41" t="n"/>
-      <c r="AS28" s="42" t="n"/>
-      <c r="AT28" s="43">
+      <c r="AS28" s="41" t="n"/>
+      <c r="AT28" s="42" t="n"/>
+      <c r="AU28" s="43">
         <f>IF(((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_thin*ROUND(K28*L28*revleg_thin,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_thin,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AU28" s="43">
+      <c r="AV28" s="43">
         <f>IF(((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_mid*ROUND(K28*L28*revleg_mid,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_mid,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AV28" s="43">
+      <c r="AW28" s="43">
         <f>IF(((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28))&lt;=0,"",VLOOKUP(B28,country_opex,7,FALSE)/((S28*pax_cap*load_full*ROUND(K28*L28*revleg_full,0))-(((battery/range_nm)*D28*ROUND(K28*L28*revleg_full,0)*VLOOKUP(B28,country_opex,3,FALSE))+V28+W28+X28+Y28+Z28)))</f>
         <v/>
       </c>
-      <c r="AW28" s="44" t="inlineStr">
-        <is>
-          <t>Bulgari Resort Dubai ~129 keys + Bulgari Yacht Club &amp; Marina; road-served. T5/low.</t>
-        </is>
-      </c>
-      <c r="AX28" s="44" t="inlineStr">
-        <is>
-          <t>OPT-IN only (R3-LAND). ~129-key resort + yacht-club members.</t>
-        </is>
-      </c>
+      <c r="AX28" s="44" t="n"/>
+      <c r="AY28" s="44" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
@@ -7104,11 +7185,11 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>Emirates Palace Marina → Saadiyat Beach Club Jetty</t>
+          <t>Bluewaters Marina → Heart of Europe — Main Marina (The World)</t>
         </is>
       </c>
       <c r="D29" s="31" t="n">
-        <v>10.4</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E29" s="26" t="n">
         <v>175</v>
@@ -7223,11 +7304,11 @@
         <v/>
       </c>
       <c r="AG29" s="31" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -7243,7 +7324,7 @@
         <v/>
       </c>
       <c r="AL29" s="34">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),FLOOR(AK29/R29,1)))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),FLOOR(AK29/R29,1)))</f>
         <v/>
       </c>
       <c r="AM29" s="38">
@@ -7251,7 +7332,7 @@
         <v/>
       </c>
       <c r="AN29" s="36">
-        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AS29="",9.9E+99,AS29),AK29/R29))</f>
+        <f>IF(OR(AG29="",R29=0),"",MIN(IF(AT29="",9.9E+99,AT29),AK29/R29))</f>
         <v/>
       </c>
       <c r="AO29" s="38">
@@ -7259,29 +7340,34 @@
         <v/>
       </c>
       <c r="AP29" s="40" t="n"/>
-      <c r="AQ29" s="41" t="n"/>
+      <c r="AQ29" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR29" s="41" t="n"/>
-      <c r="AS29" s="42" t="n"/>
-      <c r="AT29" s="43">
+      <c r="AS29" s="41" t="n"/>
+      <c r="AT29" s="42" t="n"/>
+      <c r="AU29" s="43">
         <f>IF(((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_thin*ROUND(K29*L29*revleg_thin,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_thin,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AU29" s="43">
+      <c r="AV29" s="43">
         <f>IF(((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_mid*ROUND(K29*L29*revleg_mid,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_mid,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AV29" s="43">
+      <c r="AW29" s="43">
         <f>IF(((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29))&lt;=0,"",VLOOKUP(B29,country_opex,7,FALSE)/((S29*pax_cap*load_full*ROUND(K29*L29*revleg_full,0))-(((battery/range_nm)*D29*ROUND(K29*L29*revleg_full,0)*VLOOKUP(B29,country_opex,3,FALSE))+V29+W29+X29+Y29+Z29)))</f>
         <v/>
       </c>
-      <c r="AW29" s="44" t="inlineStr">
-        <is>
-          <t>Emirates Palace&lt;-&gt;Saadiyat experiential luxury hop; both road-served. T5/low.</t>
-        </is>
-      </c>
       <c r="AX29" s="44" t="inlineStr">
         <is>
-          <t>OPT-IN only (R3-LAND: both road-served). Experiential luxury hop.</t>
+          <t>The World (Heart of Europe) boat-only offshore; greenfield. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY29" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
       </c>
     </row>
@@ -7298,15 +7384,25 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>Dubai Marina → Downtown Creek</t>
+          <t>Dubai Harbour Marina → Bulgari Yacht Club &amp; Marina</t>
         </is>
       </c>
       <c r="D30" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G30" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="H30" s="19" t="n">
         <v>1</v>
       </c>
@@ -7406,9 +7502,19 @@
         <f>((D30*O30/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D30*O30*VLOOKUP(B30,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG30" s="31" t="n"/>
-      <c r="AH30" s="32" t="n"/>
-      <c r="AI30" s="32" t="n"/>
+      <c r="AG30" s="31" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AH30" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="AI30" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="AJ30" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -7417,7 +7523,7 @@
         <v/>
       </c>
       <c r="AL30" s="34">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),FLOOR(AK30/R30,1)))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),FLOOR(AK30/R30,1)))</f>
         <v/>
       </c>
       <c r="AM30" s="38">
@@ -7425,7 +7531,7 @@
         <v/>
       </c>
       <c r="AN30" s="36">
-        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AS30="",9.9E+99,AS30),AK30/R30))</f>
+        <f>IF(OR(AG30="",R30=0),"",MIN(IF(AT30="",9.9E+99,AT30),AK30/R30))</f>
         <v/>
       </c>
       <c r="AO30" s="38">
@@ -7433,23 +7539,36 @@
         <v/>
       </c>
       <c r="AP30" s="40" t="n"/>
-      <c r="AQ30" s="41" t="n"/>
+      <c r="AQ30" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR30" s="41" t="n"/>
-      <c r="AS30" s="42" t="n"/>
-      <c r="AT30" s="43">
+      <c r="AS30" s="41" t="n"/>
+      <c r="AT30" s="42" t="n"/>
+      <c r="AU30" s="43">
         <f>IF(((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_thin*ROUND(K30*L30*revleg_thin,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_thin,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AU30" s="43">
+      <c r="AV30" s="43">
         <f>IF(((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_mid*ROUND(K30*L30*revleg_mid,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_mid,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AV30" s="43">
+      <c r="AW30" s="43">
         <f>IF(((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30))&lt;=0,"",VLOOKUP(B30,country_opex,7,FALSE)/((S30*pax_cap*load_full*ROUND(K30*L30*revleg_full,0))-(((battery/range_nm)*D30*ROUND(K30*L30*revleg_full,0)*VLOOKUP(B30,country_opex,3,FALSE))+V30+W30+X30+Y30+Z30)))</f>
         <v/>
       </c>
-      <c r="AW30" s="44" t="n"/>
-      <c r="AX30" s="44" t="n"/>
+      <c r="AX30" s="44" t="inlineStr">
+        <is>
+          <t>Bulgari Resort Dubai ~129 keys + Bulgari Yacht Club &amp; Marina; road-served. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY30" s="44" t="inlineStr">
+        <is>
+          <t>OPT-IN only (R3-LAND). ~129-key resort + yacht-club members.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
@@ -7464,15 +7583,25 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>Dubai Marina → Downtown / Dubai Creek</t>
+          <t>Emirates Palace Marina → Saadiyat Beach Club Jetty</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="32" t="n"/>
+        <v>10.4</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>175</v>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="H31" s="19" t="n">
         <v>1</v>
       </c>
@@ -7572,9 +7701,19 @@
         <f>((D31*O31/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D31*O31*VLOOKUP(B31,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG31" s="31" t="n"/>
-      <c r="AH31" s="32" t="n"/>
-      <c r="AI31" s="32" t="n"/>
+      <c r="AG31" s="31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AH31" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="AI31" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="AJ31" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -7583,7 +7722,7 @@
         <v/>
       </c>
       <c r="AL31" s="34">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),FLOOR(AK31/R31,1)))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),FLOOR(AK31/R31,1)))</f>
         <v/>
       </c>
       <c r="AM31" s="38">
@@ -7591,7 +7730,7 @@
         <v/>
       </c>
       <c r="AN31" s="36">
-        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AS31="",9.9E+99,AS31),AK31/R31))</f>
+        <f>IF(OR(AG31="",R31=0),"",MIN(IF(AT31="",9.9E+99,AT31),AK31/R31))</f>
         <v/>
       </c>
       <c r="AO31" s="38">
@@ -7599,23 +7738,36 @@
         <v/>
       </c>
       <c r="AP31" s="40" t="n"/>
-      <c r="AQ31" s="41" t="n"/>
+      <c r="AQ31" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR31" s="41" t="n"/>
-      <c r="AS31" s="42" t="n"/>
-      <c r="AT31" s="43">
+      <c r="AS31" s="41" t="n"/>
+      <c r="AT31" s="42" t="n"/>
+      <c r="AU31" s="43">
         <f>IF(((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_thin*ROUND(K31*L31*revleg_thin,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_thin,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AU31" s="43">
+      <c r="AV31" s="43">
         <f>IF(((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_mid*ROUND(K31*L31*revleg_mid,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_mid,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AV31" s="43">
+      <c r="AW31" s="43">
         <f>IF(((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31))&lt;=0,"",VLOOKUP(B31,country_opex,7,FALSE)/((S31*pax_cap*load_full*ROUND(K31*L31*revleg_full,0))-(((battery/range_nm)*D31*ROUND(K31*L31*revleg_full,0)*VLOOKUP(B31,country_opex,3,FALSE))+V31+W31+X31+Y31+Z31)))</f>
         <v/>
       </c>
-      <c r="AW31" s="44" t="n"/>
-      <c r="AX31" s="44" t="n"/>
+      <c r="AX31" s="44" t="inlineStr">
+        <is>
+          <t>Emirates Palace&lt;-&gt;Saadiyat experiential luxury hop; both road-served. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY31" s="44" t="inlineStr">
+        <is>
+          <t>OPT-IN only (R3-LAND: both road-served). Experiential luxury hop.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
@@ -7630,25 +7782,15 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>Yas Marina → Zaya Nurai Island Jetty</t>
+          <t>Fujairah → Khorfakkan Corniche / Port</t>
         </is>
       </c>
       <c r="D32" s="31" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="E32" s="26" t="n">
-        <v>175</v>
-      </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G32" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>11.4</v>
+      </c>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="32" t="n"/>
       <c r="H32" s="19" t="n">
         <v>1</v>
       </c>
@@ -7748,19 +7890,9 @@
         <f>((D32*O32/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D32*O32*VLOOKUP(B32,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG32" s="31" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AH32" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI32" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG32" s="31" t="n"/>
+      <c r="AH32" s="32" t="n"/>
+      <c r="AI32" s="32" t="n"/>
       <c r="AJ32" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -7769,7 +7901,7 @@
         <v/>
       </c>
       <c r="AL32" s="34">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),FLOOR(AK32/R32,1)))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),FLOOR(AK32/R32,1)))</f>
         <v/>
       </c>
       <c r="AM32" s="38">
@@ -7777,7 +7909,7 @@
         <v/>
       </c>
       <c r="AN32" s="36">
-        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AS32="",9.9E+99,AS32),AK32/R32))</f>
+        <f>IF(OR(AG32="",R32=0),"",MIN(IF(AT32="",9.9E+99,AT32),AK32/R32))</f>
         <v/>
       </c>
       <c r="AO32" s="38">
@@ -7785,31 +7917,28 @@
         <v/>
       </c>
       <c r="AP32" s="40" t="n"/>
-      <c r="AQ32" s="41" t="n"/>
+      <c r="AQ32" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR32" s="41" t="n"/>
-      <c r="AS32" s="42" t="n"/>
-      <c r="AT32" s="43">
+      <c r="AS32" s="41" t="n"/>
+      <c r="AT32" s="42" t="n"/>
+      <c r="AU32" s="43">
         <f>IF(((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_thin*ROUND(K32*L32*revleg_thin,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_thin,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AU32" s="43">
+      <c r="AV32" s="43">
         <f>IF(((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_mid*ROUND(K32*L32*revleg_mid,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_mid,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AV32" s="43">
+      <c r="AW32" s="43">
         <f>IF(((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32))&lt;=0,"",VLOOKUP(B32,country_opex,7,FALSE)/((S32*pax_cap*load_full*ROUND(K32*L32*revleg_full,0))-(((battery/range_nm)*D32*ROUND(K32*L32*revleg_full,0)*VLOOKUP(B32,country_opex,3,FALSE))+V32+W32+X32+Y32+Z32)))</f>
         <v/>
       </c>
-      <c r="AW32" s="44" t="inlineStr">
-        <is>
-          <t>Zaya Nurai boat-only, but real transfers depart Saadiyat (4.4nm) not Yas Marina (12.6nm) -&gt; R3-PIER. $175 modeled; demand NULL. T5/low.</t>
-        </is>
-      </c>
-      <c r="AX32" s="44" t="inlineStr">
-        <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
-        </is>
-      </c>
+      <c r="AX32" s="44" t="n"/>
+      <c r="AY32" s="44" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
@@ -7824,25 +7953,15 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Yas Marina → Saadiyat Beach Club Jetty</t>
+          <t>Dubai Harbour Marina → Nikki Beach Resort Pearl Jumeirah Jetty</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="E33" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="G33" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="32" t="n"/>
       <c r="H33" s="19" t="n">
         <v>1</v>
       </c>
@@ -7942,19 +8061,9 @@
         <f>((D33*O33/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D33*O33*VLOOKUP(B33,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG33" s="31" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AH33" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI33" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG33" s="31" t="n"/>
+      <c r="AH33" s="32" t="n"/>
+      <c r="AI33" s="32" t="n"/>
       <c r="AJ33" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -7963,7 +8072,7 @@
         <v/>
       </c>
       <c r="AL33" s="34">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),FLOOR(AK33/R33,1)))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),FLOOR(AK33/R33,1)))</f>
         <v/>
       </c>
       <c r="AM33" s="38">
@@ -7971,7 +8080,7 @@
         <v/>
       </c>
       <c r="AN33" s="36">
-        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AS33="",9.9E+99,AS33),AK33/R33))</f>
+        <f>IF(OR(AG33="",R33=0),"",MIN(IF(AT33="",9.9E+99,AT33),AK33/R33))</f>
         <v/>
       </c>
       <c r="AO33" s="38">
@@ -7979,31 +8088,28 @@
         <v/>
       </c>
       <c r="AP33" s="40" t="n"/>
-      <c r="AQ33" s="41" t="n"/>
+      <c r="AQ33" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR33" s="41" t="n"/>
-      <c r="AS33" s="42" t="n"/>
-      <c r="AT33" s="43">
+      <c r="AS33" s="41" t="n"/>
+      <c r="AT33" s="42" t="n"/>
+      <c r="AU33" s="43">
         <f>IF(((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_thin*ROUND(K33*L33*revleg_thin,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_thin,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AU33" s="43">
+      <c r="AV33" s="43">
         <f>IF(((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_mid*ROUND(K33*L33*revleg_mid,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_mid,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AV33" s="43">
+      <c r="AW33" s="43">
         <f>IF(((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33))&lt;=0,"",VLOOKUP(B33,country_opex,7,FALSE)/((S33*pax_cap*load_full*ROUND(K33*L33*revleg_full,0))-(((battery/range_nm)*D33*ROUND(K33*L33*revleg_full,0)*VLOOKUP(B33,country_opex,3,FALSE))+V33+W33+X33+Y33+Z33)))</f>
         <v/>
       </c>
-      <c r="AW33" s="44" t="inlineStr">
-        <is>
-          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. AD leisure-island network; no published AD water-taxi tariff; anchored on Dubai RTA premium ladder.</t>
-        </is>
-      </c>
-      <c r="AX33" s="44" t="inlineStr">
-        <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
-        </is>
-      </c>
+      <c r="AX33" s="44" t="n"/>
+      <c r="AY33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
@@ -8018,25 +8124,15 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Dibba Marina (Fujairah) → Khorfakkan Corniche / Port (Sharjah enclave)</t>
+          <t>Ras Al Khaimah → ميناء صيادين غليلة</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E34" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="F34" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G34" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="32" t="n"/>
       <c r="H34" s="19" t="n">
         <v>1</v>
       </c>
@@ -8136,19 +8232,9 @@
         <f>((D34*O34/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D34*O34*VLOOKUP(B34,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG34" s="31" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AH34" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI34" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG34" s="31" t="n"/>
+      <c r="AH34" s="32" t="n"/>
+      <c r="AI34" s="32" t="n"/>
       <c r="AJ34" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -8157,7 +8243,7 @@
         <v/>
       </c>
       <c r="AL34" s="34">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),FLOOR(AK34/R34,1)))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),FLOOR(AK34/R34,1)))</f>
         <v/>
       </c>
       <c r="AM34" s="38">
@@ -8165,7 +8251,7 @@
         <v/>
       </c>
       <c r="AN34" s="36">
-        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AS34="",9.9E+99,AS34),AK34/R34))</f>
+        <f>IF(OR(AG34="",R34=0),"",MIN(IF(AT34="",9.9E+99,AT34),AK34/R34))</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -8173,31 +8259,28 @@
         <v/>
       </c>
       <c r="AP34" s="40" t="n"/>
-      <c r="AQ34" s="41" t="n"/>
+      <c r="AQ34" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR34" s="41" t="n"/>
-      <c r="AS34" s="42" t="n"/>
-      <c r="AT34" s="43">
+      <c r="AS34" s="41" t="n"/>
+      <c r="AT34" s="42" t="n"/>
+      <c r="AU34" s="43">
         <f>IF(((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_thin*ROUND(K34*L34*revleg_thin,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_thin,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AU34" s="43">
+      <c r="AV34" s="43">
         <f>IF(((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_mid*ROUND(K34*L34*revleg_mid,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_mid,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AV34" s="43">
+      <c r="AW34" s="43">
         <f>IF(((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34))&lt;=0,"",VLOOKUP(B34,country_opex,7,FALSE)/((S34*pax_cap*load_full*ROUND(K34*L34*revleg_full,0))-(((battery/range_nm)*D34*ROUND(K34*L34*revleg_full,0)*VLOOKUP(B34,country_opex,3,FALSE))+V34+W34+X34+Y34+Z34)))</f>
         <v/>
       </c>
-      <c r="AW34" s="44" t="inlineStr">
-        <is>
-          <t>Fujairah east-coast day-trip boats: Dibba/Khor Fakkan dhow &amp; speedboat tours AED 140-210/pax (Instagram/Tripadvisor/Viator 2025); Musandam dhow cruises similar.</t>
-        </is>
-      </c>
-      <c r="AX34" s="44" t="inlineStr">
-        <is>
-          <t>Fujairah arrivals crossed 340,000 (+22% YoY), 209 hotels, 70-100% occ (UAE Ministry/Fujairah Tourism); east-coast diving/Musandam day-trips genuinely water-based.</t>
-        </is>
-      </c>
+      <c r="AX34" s="44" t="n"/>
+      <c r="AY34" s="44" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
@@ -8212,25 +8295,15 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Al Khan Lagoon mouth</t>
+          <t>Dubai Marina → Downtown / Dubai Creek</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E35" s="26" t="n">
-        <v>85</v>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G35" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="32" t="n"/>
       <c r="H35" s="19" t="n">
         <v>1</v>
       </c>
@@ -8330,19 +8403,9 @@
         <f>((D35*O35/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D35*O35*VLOOKUP(B35,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG35" s="31" t="n">
-        <v>40000</v>
-      </c>
-      <c r="AH35" s="32" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="AI35" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG35" s="31" t="n"/>
+      <c r="AH35" s="32" t="n"/>
+      <c r="AI35" s="32" t="n"/>
       <c r="AJ35" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -8351,7 +8414,7 @@
         <v/>
       </c>
       <c r="AL35" s="34">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),FLOOR(AK35/R35,1)))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),FLOOR(AK35/R35,1)))</f>
         <v/>
       </c>
       <c r="AM35" s="38">
@@ -8359,7 +8422,7 @@
         <v/>
       </c>
       <c r="AN35" s="36">
-        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AS35="",9.9E+99,AS35),AK35/R35))</f>
+        <f>IF(OR(AG35="",R35=0),"",MIN(IF(AT35="",9.9E+99,AT35),AK35/R35))</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -8367,31 +8430,28 @@
         <v/>
       </c>
       <c r="AP35" s="40" t="n"/>
-      <c r="AQ35" s="41" t="n"/>
+      <c r="AQ35" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR35" s="41" t="n"/>
-      <c r="AS35" s="42" t="n"/>
-      <c r="AT35" s="43">
+      <c r="AS35" s="41" t="n"/>
+      <c r="AT35" s="42" t="n"/>
+      <c r="AU35" s="43">
         <f>IF(((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_thin*ROUND(K35*L35*revleg_thin,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_thin,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AU35" s="43">
+      <c r="AV35" s="43">
         <f>IF(((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_mid*ROUND(K35*L35*revleg_mid,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_mid,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AV35" s="43">
+      <c r="AW35" s="43">
         <f>IF(((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35))&lt;=0,"",VLOOKUP(B35,country_opex,7,FALSE)/((S35*pax_cap*load_full*ROUND(K35*L35*revleg_full,0))-(((battery/range_nm)*D35*ROUND(K35*L35*revleg_full,0)*VLOOKUP(B35,country_opex,3,FALSE))+V35+W35+X35+Y35+Z35)))</f>
         <v/>
       </c>
-      <c r="AW35" s="44" t="inlineStr">
-        <is>
-          <t>Dubai-Sharjah Ferry Gold AED 25 subsidized-commuter (R5-EXT). Premium per-seat $85 modeled (between subsidized ferry and charter). T5/low.</t>
-        </is>
-      </c>
-      <c r="AX35" s="44" t="inlineStr">
-        <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
-        </is>
-      </c>
+      <c r="AX35" s="44" t="n"/>
+      <c r="AY35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
@@ -8406,11 +8466,11 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Dubai → Abu Dhabi (Corniche)</t>
+          <t>Dubai Marina → Downtown Creek</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
-        <v>55.8</v>
+        <v>12</v>
       </c>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="32" t="n"/>
@@ -8525,7 +8585,7 @@
         <v/>
       </c>
       <c r="AL36" s="34">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),FLOOR(AK36/R36,1)))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),FLOOR(AK36/R36,1)))</f>
         <v/>
       </c>
       <c r="AM36" s="38">
@@ -8533,7 +8593,7 @@
         <v/>
       </c>
       <c r="AN36" s="36">
-        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AS36="",9.9E+99,AS36),AK36/R36))</f>
+        <f>IF(OR(AG36="",R36=0),"",MIN(IF(AT36="",9.9E+99,AT36),AK36/R36))</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -8541,23 +8601,28 @@
         <v/>
       </c>
       <c r="AP36" s="40" t="n"/>
-      <c r="AQ36" s="41" t="n"/>
+      <c r="AQ36" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR36" s="41" t="n"/>
-      <c r="AS36" s="42" t="n"/>
-      <c r="AT36" s="43">
+      <c r="AS36" s="41" t="n"/>
+      <c r="AT36" s="42" t="n"/>
+      <c r="AU36" s="43">
         <f>IF(((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_thin*ROUND(K36*L36*revleg_thin,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_thin,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AU36" s="43">
+      <c r="AV36" s="43">
         <f>IF(((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_mid*ROUND(K36*L36*revleg_mid,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_mid,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AV36" s="43">
+      <c r="AW36" s="43">
         <f>IF(((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36))&lt;=0,"",VLOOKUP(B36,country_opex,7,FALSE)/((S36*pax_cap*load_full*ROUND(K36*L36*revleg_full,0))-(((battery/range_nm)*D36*ROUND(K36*L36*revleg_full,0)*VLOOKUP(B36,country_opex,3,FALSE))+V36+W36+X36+Y36+Z36)))</f>
         <v/>
       </c>
-      <c r="AW36" s="44" t="n"/>
       <c r="AX36" s="44" t="n"/>
+      <c r="AY36" s="44" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
@@ -8572,11 +8637,11 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>Dubai Marina → Abu Dhabi Corniche</t>
+          <t>Yas Marina → Four Seasons Al Maryah Jetty</t>
         </is>
       </c>
       <c r="D37" s="31" t="n">
-        <v>55.8</v>
+        <v>12.4</v>
       </c>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="32" t="n"/>
@@ -8691,7 +8756,7 @@
         <v/>
       </c>
       <c r="AL37" s="34">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),FLOOR(AK37/R37,1)))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),FLOOR(AK37/R37,1)))</f>
         <v/>
       </c>
       <c r="AM37" s="38">
@@ -8699,7 +8764,7 @@
         <v/>
       </c>
       <c r="AN37" s="36">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AS37="",9.9E+99,AS37),AK37/R37))</f>
+        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),AK37/R37))</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -8707,23 +8772,28 @@
         <v/>
       </c>
       <c r="AP37" s="40" t="n"/>
-      <c r="AQ37" s="41" t="n"/>
+      <c r="AQ37" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR37" s="41" t="n"/>
-      <c r="AS37" s="42" t="n"/>
-      <c r="AT37" s="43">
+      <c r="AS37" s="41" t="n"/>
+      <c r="AT37" s="42" t="n"/>
+      <c r="AU37" s="43">
         <f>IF(((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AU37" s="43">
+      <c r="AV37" s="43">
         <f>IF(((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AV37" s="43">
+      <c r="AW37" s="43">
         <f>IF(((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
         <v/>
       </c>
-      <c r="AW37" s="44" t="n"/>
       <c r="AX37" s="44" t="n"/>
+      <c r="AY37" s="44" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
@@ -8738,14 +8808,14 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
+          <t>Yas Marina → Zaya Nurai Island Jetty</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
-        <v>56</v>
+        <v>12.6</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
@@ -8857,16 +8927,16 @@
         <v/>
       </c>
       <c r="AG38" s="31" t="n">
-        <v>60000</v>
+        <v>15000</v>
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AJ38" s="39" t="n">
@@ -8877,7 +8947,7 @@
         <v/>
       </c>
       <c r="AL38" s="34">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),FLOOR(AK38/R38,1)))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),FLOOR(AK38/R38,1)))</f>
         <v/>
       </c>
       <c r="AM38" s="38">
@@ -8885,7 +8955,7 @@
         <v/>
       </c>
       <c r="AN38" s="36">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AS38="",9.9E+99,AS38),AK38/R38))</f>
+        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),AK38/R38))</f>
         <v/>
       </c>
       <c r="AO38" s="38">
@@ -8893,29 +8963,34 @@
         <v/>
       </c>
       <c r="AP38" s="40" t="n"/>
-      <c r="AQ38" s="41" t="n"/>
+      <c r="AQ38" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR38" s="41" t="n"/>
-      <c r="AS38" s="42" t="n"/>
-      <c r="AT38" s="43">
+      <c r="AS38" s="41" t="n"/>
+      <c r="AT38" s="42" t="n"/>
+      <c r="AU38" s="43">
         <f>IF(((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AU38" s="43">
+      <c r="AV38" s="43">
         <f>IF(((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AV38" s="43">
+      <c r="AW38" s="43">
         <f>IF(((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
         <v/>
       </c>
-      <c r="AW38" s="44" t="inlineStr">
-        <is>
-          <t>Wynn Al Marjan (first UAE gaming resort) opens early 2027: 1,217 rooms + 297 residences. No marine transfer today. T5/low - greenfield.</t>
-        </is>
-      </c>
       <c r="AX38" s="44" t="inlineStr">
         <is>
-          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
+          <t>Zaya Nurai boat-only, but real transfers depart Saadiyat (4.4nm) not Yas Marina (12.6nm) -&gt; R3-PIER. $175 modeled; demand NULL. T5/low.</t>
+        </is>
+      </c>
+      <c r="AY38" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
         </is>
       </c>
     </row>
@@ -8932,18 +9007,18 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>Dubai Harbour Marina → Marina Mall / Breakwater Marina</t>
+          <t>Yas Marina → Saadiyat Beach Club Jetty</t>
         </is>
       </c>
       <c r="D39" s="31" t="n">
-        <v>59.8</v>
+        <v>13</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
@@ -9051,11 +9126,11 @@
         <v/>
       </c>
       <c r="AG39" s="31" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
@@ -9071,7 +9146,7 @@
         <v/>
       </c>
       <c r="AL39" s="34">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),FLOOR(AK39/R39,1)))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),FLOOR(AK39/R39,1)))</f>
         <v/>
       </c>
       <c r="AM39" s="38">
@@ -9079,7 +9154,7 @@
         <v/>
       </c>
       <c r="AN39" s="36">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AS39="",9.9E+99,AS39),AK39/R39))</f>
+        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),AK39/R39))</f>
         <v/>
       </c>
       <c r="AO39" s="38">
@@ -9087,162 +9162,2346 @@
         <v/>
       </c>
       <c r="AP39" s="40" t="n"/>
-      <c r="AQ39" s="41" t="n"/>
+      <c r="AQ39" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR39" s="41" t="n"/>
-      <c r="AS39" s="42" t="n"/>
-      <c r="AT39" s="43">
+      <c r="AS39" s="41" t="n"/>
+      <c r="AT39" s="42" t="n"/>
+      <c r="AU39" s="43">
         <f>IF(((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AU39" s="43">
+      <c r="AV39" s="43">
         <f>IF(((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AV39" s="43">
+      <c r="AW39" s="43">
         <f>IF(((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
         <v/>
       </c>
-      <c r="AW39" s="44" t="inlineStr">
+      <c r="AX39" s="44" t="inlineStr">
+        <is>
+          <t>RTA/Dubai-Ferry official ladder (R-RTA, T1): Water Taxi on-demand single AED 150/pax = $40.8; Dubai Ferry Gold AED 75 = $20.4, Silver AED 50 = $13.6; Water Bus AED 7; Abra AED 1. dubai-ferry.com / rta.ae 2025/26. AD leisure-island network; no published AD water-taxi tariff; anchored on Dubai RTA premium ladder.</t>
+        </is>
+      </c>
+      <c r="AY39" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — tier-based addressable pool derived from sourcing wave anchors (hotel keys × occ × shuttle adoption, marina activity, RTA marine baseline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Al Khan Lagoon mouth</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="32" t="n"/>
+      <c r="H40" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="33">
+        <f>60*D40/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J40" s="33">
+        <f>I40+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K40" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J40,1))</f>
+        <v/>
+      </c>
+      <c r="L40" s="34">
+        <f>ROUND(365*mech_uptime*H40,0)</f>
+        <v/>
+      </c>
+      <c r="M40" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N40" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O40" s="34">
+        <f>ROUND(K40*L40*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P40" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q40" s="36">
+        <f>pax_cap*P40</f>
+        <v/>
+      </c>
+      <c r="R40" s="34">
+        <f>Q40*O40</f>
+        <v/>
+      </c>
+      <c r="S40" s="37">
+        <f>E40*discount</f>
+        <v/>
+      </c>
+      <c r="T40" s="38">
+        <f>S40*R40</f>
+        <v/>
+      </c>
+      <c r="U40" s="38">
+        <f>(battery/range_nm)*D40*O40*VLOOKUP(B40,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V40" s="38">
+        <f>VLOOKUP(B40,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W40" s="38">
+        <f>VLOOKUP(B40,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X40" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y40" s="38">
+        <f>VLOOKUP(B40,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z40" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA40" s="38">
+        <f>U40+V40+W40+X40+Y40+Z40</f>
+        <v/>
+      </c>
+      <c r="AB40" s="38">
+        <f>VLOOKUP(B40,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC40" s="38">
+        <f>T40-AA40</f>
+        <v/>
+      </c>
+      <c r="AD40" s="35">
+        <f>IF(T40=0,"",AC40/T40)</f>
+        <v/>
+      </c>
+      <c r="AE40" s="36">
+        <f>IF(AC40&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/AC40)</f>
+        <v/>
+      </c>
+      <c r="AF40" s="33">
+        <f>((D40*O40/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D40*O40*VLOOKUP(B40,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG40" s="31" t="n"/>
+      <c r="AH40" s="32" t="n"/>
+      <c r="AI40" s="32" t="n"/>
+      <c r="AJ40" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK40" s="34">
+        <f>IF(AG40="","",AG40*AJ40)</f>
+        <v/>
+      </c>
+      <c r="AL40" s="34">
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),FLOOR(AK40/R40,1)))</f>
+        <v/>
+      </c>
+      <c r="AM40" s="38">
+        <f>IF(AL40="","",AL40*T40)</f>
+        <v/>
+      </c>
+      <c r="AN40" s="36">
+        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),AK40/R40))</f>
+        <v/>
+      </c>
+      <c r="AO40" s="38">
+        <f>IF(AN40="","",AN40*T40)</f>
+        <v/>
+      </c>
+      <c r="AP40" s="40" t="n"/>
+      <c r="AQ40" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR40" s="41" t="n"/>
+      <c r="AS40" s="41" t="n"/>
+      <c r="AT40" s="42" t="n"/>
+      <c r="AU40" s="43">
+        <f>IF(((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
+        <v/>
+      </c>
+      <c r="AV40" s="43">
+        <f>IF(((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
+        <v/>
+      </c>
+      <c r="AW40" s="43">
+        <f>IF(((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
+        <v/>
+      </c>
+      <c r="AX40" s="44" t="n"/>
+      <c r="AY40" s="44" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>Dibba Marina (Fujairah) → Khorfakkan Corniche / Port (Sharjah enclave)</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G41" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="33">
+        <f>60*D41/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J41" s="33">
+        <f>I41+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K41" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J41,1))</f>
+        <v/>
+      </c>
+      <c r="L41" s="34">
+        <f>ROUND(365*mech_uptime*H41,0)</f>
+        <v/>
+      </c>
+      <c r="M41" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N41" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O41" s="34">
+        <f>ROUND(K41*L41*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P41" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q41" s="36">
+        <f>pax_cap*P41</f>
+        <v/>
+      </c>
+      <c r="R41" s="34">
+        <f>Q41*O41</f>
+        <v/>
+      </c>
+      <c r="S41" s="37">
+        <f>E41*discount</f>
+        <v/>
+      </c>
+      <c r="T41" s="38">
+        <f>S41*R41</f>
+        <v/>
+      </c>
+      <c r="U41" s="38">
+        <f>(battery/range_nm)*D41*O41*VLOOKUP(B41,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V41" s="38">
+        <f>VLOOKUP(B41,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W41" s="38">
+        <f>VLOOKUP(B41,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X41" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y41" s="38">
+        <f>VLOOKUP(B41,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z41" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA41" s="38">
+        <f>U41+V41+W41+X41+Y41+Z41</f>
+        <v/>
+      </c>
+      <c r="AB41" s="38">
+        <f>VLOOKUP(B41,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC41" s="38">
+        <f>T41-AA41</f>
+        <v/>
+      </c>
+      <c r="AD41" s="35">
+        <f>IF(T41=0,"",AC41/T41)</f>
+        <v/>
+      </c>
+      <c r="AE41" s="36">
+        <f>IF(AC41&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/AC41)</f>
+        <v/>
+      </c>
+      <c r="AF41" s="33">
+        <f>((D41*O41/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D41*O41*VLOOKUP(B41,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG41" s="31" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AH41" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI41" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AJ41" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK41" s="34">
+        <f>IF(AG41="","",AG41*AJ41)</f>
+        <v/>
+      </c>
+      <c r="AL41" s="34">
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),FLOOR(AK41/R41,1)))</f>
+        <v/>
+      </c>
+      <c r="AM41" s="38">
+        <f>IF(AL41="","",AL41*T41)</f>
+        <v/>
+      </c>
+      <c r="AN41" s="36">
+        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),AK41/R41))</f>
+        <v/>
+      </c>
+      <c r="AO41" s="38">
+        <f>IF(AN41="","",AN41*T41)</f>
+        <v/>
+      </c>
+      <c r="AP41" s="40" t="n"/>
+      <c r="AQ41" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR41" s="41" t="n"/>
+      <c r="AS41" s="41" t="n"/>
+      <c r="AT41" s="42" t="n"/>
+      <c r="AU41" s="43">
+        <f>IF(((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
+        <v/>
+      </c>
+      <c r="AV41" s="43">
+        <f>IF(((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
+        <v/>
+      </c>
+      <c r="AW41" s="43">
+        <f>IF(((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
+        <v/>
+      </c>
+      <c r="AX41" s="44" t="inlineStr">
+        <is>
+          <t>Fujairah east-coast day-trip boats: Dibba/Khor Fakkan dhow &amp; speedboat tours AED 140-210/pax (Instagram/Tripadvisor/Viator 2025); Musandam dhow cruises similar.</t>
+        </is>
+      </c>
+      <c r="AY41" s="44" t="inlineStr">
+        <is>
+          <t>Fujairah arrivals crossed 340,000 (+22% YoY), 209 hotels, 70-100% occ (UAE Ministry/Fujairah Tourism); east-coast diving/Musandam day-trips genuinely water-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Al Khan Lagoon mouth</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="F42" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="33">
+        <f>60*D42/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J42" s="33">
+        <f>I42+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K42" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
+        <v/>
+      </c>
+      <c r="L42" s="34">
+        <f>ROUND(365*mech_uptime*H42,0)</f>
+        <v/>
+      </c>
+      <c r="M42" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N42" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O42" s="34">
+        <f>ROUND(K42*L42*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P42" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q42" s="36">
+        <f>pax_cap*P42</f>
+        <v/>
+      </c>
+      <c r="R42" s="34">
+        <f>Q42*O42</f>
+        <v/>
+      </c>
+      <c r="S42" s="37">
+        <f>E42*discount</f>
+        <v/>
+      </c>
+      <c r="T42" s="38">
+        <f>S42*R42</f>
+        <v/>
+      </c>
+      <c r="U42" s="38">
+        <f>(battery/range_nm)*D42*O42*VLOOKUP(B42,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V42" s="38">
+        <f>VLOOKUP(B42,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W42" s="38">
+        <f>VLOOKUP(B42,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X42" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y42" s="38">
+        <f>VLOOKUP(B42,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z42" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA42" s="38">
+        <f>U42+V42+W42+X42+Y42+Z42</f>
+        <v/>
+      </c>
+      <c r="AB42" s="38">
+        <f>VLOOKUP(B42,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC42" s="38">
+        <f>T42-AA42</f>
+        <v/>
+      </c>
+      <c r="AD42" s="35">
+        <f>IF(T42=0,"",AC42/T42)</f>
+        <v/>
+      </c>
+      <c r="AE42" s="36">
+        <f>IF(AC42&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/AC42)</f>
+        <v/>
+      </c>
+      <c r="AF42" s="33">
+        <f>((D42*O42/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D42*O42*VLOOKUP(B42,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG42" s="31" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AH42" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="AI42" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AJ42" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK42" s="34">
+        <f>IF(AG42="","",AG42*AJ42)</f>
+        <v/>
+      </c>
+      <c r="AL42" s="34">
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),FLOOR(AK42/R42,1)))</f>
+        <v/>
+      </c>
+      <c r="AM42" s="38">
+        <f>IF(AL42="","",AL42*T42)</f>
+        <v/>
+      </c>
+      <c r="AN42" s="36">
+        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),AK42/R42))</f>
+        <v/>
+      </c>
+      <c r="AO42" s="38">
+        <f>IF(AN42="","",AN42*T42)</f>
+        <v/>
+      </c>
+      <c r="AP42" s="40" t="n"/>
+      <c r="AQ42" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR42" s="41" t="n"/>
+      <c r="AS42" s="41" t="n"/>
+      <c r="AT42" s="42" t="n"/>
+      <c r="AU42" s="43">
+        <f>IF(((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
+        <v/>
+      </c>
+      <c r="AV42" s="43">
+        <f>IF(((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
+        <v/>
+      </c>
+      <c r="AW42" s="43">
+        <f>IF(((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
+        <v/>
+      </c>
+      <c r="AX42" s="44" t="inlineStr">
+        <is>
+          <t>Dubai-Sharjah Ferry Gold AED 25 subsidized-commuter (R5-EXT). Premium per-seat $85 modeled (between subsidized ferry and charter). T5/low.</t>
+        </is>
+      </c>
+      <c r="AY42" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="33">
+        <f>60*D43/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J43" s="33">
+        <f>I43+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K43" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
+        <v/>
+      </c>
+      <c r="L43" s="34">
+        <f>ROUND(365*mech_uptime*H43,0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N43" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O43" s="34">
+        <f>ROUND(K43*L43*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P43" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q43" s="36">
+        <f>pax_cap*P43</f>
+        <v/>
+      </c>
+      <c r="R43" s="34">
+        <f>Q43*O43</f>
+        <v/>
+      </c>
+      <c r="S43" s="37">
+        <f>E43*discount</f>
+        <v/>
+      </c>
+      <c r="T43" s="38">
+        <f>S43*R43</f>
+        <v/>
+      </c>
+      <c r="U43" s="38">
+        <f>(battery/range_nm)*D43*O43*VLOOKUP(B43,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V43" s="38">
+        <f>VLOOKUP(B43,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W43" s="38">
+        <f>VLOOKUP(B43,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X43" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y43" s="38">
+        <f>VLOOKUP(B43,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z43" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA43" s="38">
+        <f>U43+V43+W43+X43+Y43+Z43</f>
+        <v/>
+      </c>
+      <c r="AB43" s="38">
+        <f>VLOOKUP(B43,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC43" s="38">
+        <f>T43-AA43</f>
+        <v/>
+      </c>
+      <c r="AD43" s="35">
+        <f>IF(T43=0,"",AC43/T43)</f>
+        <v/>
+      </c>
+      <c r="AE43" s="36">
+        <f>IF(AC43&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/AC43)</f>
+        <v/>
+      </c>
+      <c r="AF43" s="33">
+        <f>((D43*O43/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D43*O43*VLOOKUP(B43,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG43" s="31" t="n"/>
+      <c r="AH43" s="32" t="n"/>
+      <c r="AI43" s="32" t="n"/>
+      <c r="AJ43" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK43" s="34">
+        <f>IF(AG43="","",AG43*AJ43)</f>
+        <v/>
+      </c>
+      <c r="AL43" s="34">
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),FLOOR(AK43/R43,1)))</f>
+        <v/>
+      </c>
+      <c r="AM43" s="38">
+        <f>IF(AL43="","",AL43*T43)</f>
+        <v/>
+      </c>
+      <c r="AN43" s="36">
+        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),AK43/R43))</f>
+        <v/>
+      </c>
+      <c r="AO43" s="38">
+        <f>IF(AN43="","",AN43*T43)</f>
+        <v/>
+      </c>
+      <c r="AP43" s="40" t="n"/>
+      <c r="AQ43" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR43" s="41" t="n"/>
+      <c r="AS43" s="41" t="n"/>
+      <c r="AT43" s="42" t="n"/>
+      <c r="AU43" s="43">
+        <f>IF(((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
+        <v/>
+      </c>
+      <c r="AV43" s="43">
+        <f>IF(((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
+        <v/>
+      </c>
+      <c r="AW43" s="43">
+        <f>IF(((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
+        <v/>
+      </c>
+      <c r="AX43" s="44" t="n"/>
+      <c r="AY43" s="44" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>Dubai → Abu Dhabi (Corniche)</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="32" t="n"/>
+      <c r="H44" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="33">
+        <f>60*D44/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J44" s="33">
+        <f>I44+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K44" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
+        <v/>
+      </c>
+      <c r="L44" s="34">
+        <f>ROUND(365*mech_uptime*H44,0)</f>
+        <v/>
+      </c>
+      <c r="M44" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N44" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O44" s="34">
+        <f>ROUND(K44*L44*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P44" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q44" s="36">
+        <f>pax_cap*P44</f>
+        <v/>
+      </c>
+      <c r="R44" s="34">
+        <f>Q44*O44</f>
+        <v/>
+      </c>
+      <c r="S44" s="37">
+        <f>E44*discount</f>
+        <v/>
+      </c>
+      <c r="T44" s="38">
+        <f>S44*R44</f>
+        <v/>
+      </c>
+      <c r="U44" s="38">
+        <f>(battery/range_nm)*D44*O44*VLOOKUP(B44,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V44" s="38">
+        <f>VLOOKUP(B44,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W44" s="38">
+        <f>VLOOKUP(B44,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X44" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y44" s="38">
+        <f>VLOOKUP(B44,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z44" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA44" s="38">
+        <f>U44+V44+W44+X44+Y44+Z44</f>
+        <v/>
+      </c>
+      <c r="AB44" s="38">
+        <f>VLOOKUP(B44,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC44" s="38">
+        <f>T44-AA44</f>
+        <v/>
+      </c>
+      <c r="AD44" s="35">
+        <f>IF(T44=0,"",AC44/T44)</f>
+        <v/>
+      </c>
+      <c r="AE44" s="36">
+        <f>IF(AC44&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/AC44)</f>
+        <v/>
+      </c>
+      <c r="AF44" s="33">
+        <f>((D44*O44/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D44*O44*VLOOKUP(B44,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG44" s="31" t="n"/>
+      <c r="AH44" s="32" t="n"/>
+      <c r="AI44" s="32" t="n"/>
+      <c r="AJ44" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK44" s="34">
+        <f>IF(AG44="","",AG44*AJ44)</f>
+        <v/>
+      </c>
+      <c r="AL44" s="34">
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),FLOOR(AK44/R44,1)))</f>
+        <v/>
+      </c>
+      <c r="AM44" s="38">
+        <f>IF(AL44="","",AL44*T44)</f>
+        <v/>
+      </c>
+      <c r="AN44" s="36">
+        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),AK44/R44))</f>
+        <v/>
+      </c>
+      <c r="AO44" s="38">
+        <f>IF(AN44="","",AN44*T44)</f>
+        <v/>
+      </c>
+      <c r="AP44" s="40" t="n"/>
+      <c r="AQ44" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR44" s="41" t="n"/>
+      <c r="AS44" s="41" t="n"/>
+      <c r="AT44" s="42" t="n"/>
+      <c r="AU44" s="43">
+        <f>IF(((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
+        <v/>
+      </c>
+      <c r="AV44" s="43">
+        <f>IF(((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
+        <v/>
+      </c>
+      <c r="AW44" s="43">
+        <f>IF(((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
+        <v/>
+      </c>
+      <c r="AX44" s="44" t="n"/>
+      <c r="AY44" s="44" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>Dubai → Abu Dhabi (Corniche)</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="32" t="n"/>
+      <c r="H45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="33">
+        <f>60*D45/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J45" s="33">
+        <f>I45+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K45" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
+        <v/>
+      </c>
+      <c r="L45" s="34">
+        <f>ROUND(365*mech_uptime*H45,0)</f>
+        <v/>
+      </c>
+      <c r="M45" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N45" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O45" s="34">
+        <f>ROUND(K45*L45*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P45" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q45" s="36">
+        <f>pax_cap*P45</f>
+        <v/>
+      </c>
+      <c r="R45" s="34">
+        <f>Q45*O45</f>
+        <v/>
+      </c>
+      <c r="S45" s="37">
+        <f>E45*discount</f>
+        <v/>
+      </c>
+      <c r="T45" s="38">
+        <f>S45*R45</f>
+        <v/>
+      </c>
+      <c r="U45" s="38">
+        <f>(battery/range_nm)*D45*O45*VLOOKUP(B45,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V45" s="38">
+        <f>VLOOKUP(B45,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W45" s="38">
+        <f>VLOOKUP(B45,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X45" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y45" s="38">
+        <f>VLOOKUP(B45,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z45" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA45" s="38">
+        <f>U45+V45+W45+X45+Y45+Z45</f>
+        <v/>
+      </c>
+      <c r="AB45" s="38">
+        <f>VLOOKUP(B45,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC45" s="38">
+        <f>T45-AA45</f>
+        <v/>
+      </c>
+      <c r="AD45" s="35">
+        <f>IF(T45=0,"",AC45/T45)</f>
+        <v/>
+      </c>
+      <c r="AE45" s="36">
+        <f>IF(AC45&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/AC45)</f>
+        <v/>
+      </c>
+      <c r="AF45" s="33">
+        <f>((D45*O45/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D45*O45*VLOOKUP(B45,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG45" s="31" t="n"/>
+      <c r="AH45" s="32" t="n"/>
+      <c r="AI45" s="32" t="n"/>
+      <c r="AJ45" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK45" s="34">
+        <f>IF(AG45="","",AG45*AJ45)</f>
+        <v/>
+      </c>
+      <c r="AL45" s="34">
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),FLOOR(AK45/R45,1)))</f>
+        <v/>
+      </c>
+      <c r="AM45" s="38">
+        <f>IF(AL45="","",AL45*T45)</f>
+        <v/>
+      </c>
+      <c r="AN45" s="36">
+        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),AK45/R45))</f>
+        <v/>
+      </c>
+      <c r="AO45" s="38">
+        <f>IF(AN45="","",AN45*T45)</f>
+        <v/>
+      </c>
+      <c r="AP45" s="40" t="n"/>
+      <c r="AQ45" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR45" s="41" t="n"/>
+      <c r="AS45" s="41" t="n"/>
+      <c r="AT45" s="42" t="n"/>
+      <c r="AU45" s="43">
+        <f>IF(((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
+        <v/>
+      </c>
+      <c r="AV45" s="43">
+        <f>IF(((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
+        <v/>
+      </c>
+      <c r="AW45" s="43">
+        <f>IF(((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
+        <v/>
+      </c>
+      <c r="AX45" s="44" t="n"/>
+      <c r="AY45" s="44" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Marina → Abu Dhabi Corniche</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="32" t="n"/>
+      <c r="G46" s="32" t="n"/>
+      <c r="H46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="33">
+        <f>60*D46/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J46" s="33">
+        <f>I46+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K46" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
+        <v/>
+      </c>
+      <c r="L46" s="34">
+        <f>ROUND(365*mech_uptime*H46,0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N46" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O46" s="34">
+        <f>ROUND(K46*L46*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P46" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q46" s="36">
+        <f>pax_cap*P46</f>
+        <v/>
+      </c>
+      <c r="R46" s="34">
+        <f>Q46*O46</f>
+        <v/>
+      </c>
+      <c r="S46" s="37">
+        <f>E46*discount</f>
+        <v/>
+      </c>
+      <c r="T46" s="38">
+        <f>S46*R46</f>
+        <v/>
+      </c>
+      <c r="U46" s="38">
+        <f>(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V46" s="38">
+        <f>VLOOKUP(B46,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W46" s="38">
+        <f>VLOOKUP(B46,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X46" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y46" s="38">
+        <f>VLOOKUP(B46,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z46" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA46" s="38">
+        <f>U46+V46+W46+X46+Y46+Z46</f>
+        <v/>
+      </c>
+      <c r="AB46" s="38">
+        <f>VLOOKUP(B46,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC46" s="38">
+        <f>T46-AA46</f>
+        <v/>
+      </c>
+      <c r="AD46" s="35">
+        <f>IF(T46=0,"",AC46/T46)</f>
+        <v/>
+      </c>
+      <c r="AE46" s="36">
+        <f>IF(AC46&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/AC46)</f>
+        <v/>
+      </c>
+      <c r="AF46" s="33">
+        <f>((D46*O46/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG46" s="31" t="n"/>
+      <c r="AH46" s="32" t="n"/>
+      <c r="AI46" s="32" t="n"/>
+      <c r="AJ46" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK46" s="34">
+        <f>IF(AG46="","",AG46*AJ46)</f>
+        <v/>
+      </c>
+      <c r="AL46" s="34">
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),FLOOR(AK46/R46,1)))</f>
+        <v/>
+      </c>
+      <c r="AM46" s="38">
+        <f>IF(AL46="","",AL46*T46)</f>
+        <v/>
+      </c>
+      <c r="AN46" s="36">
+        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),AK46/R46))</f>
+        <v/>
+      </c>
+      <c r="AO46" s="38">
+        <f>IF(AN46="","",AN46*T46)</f>
+        <v/>
+      </c>
+      <c r="AP46" s="40" t="n"/>
+      <c r="AQ46" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR46" s="41" t="n"/>
+      <c r="AS46" s="41" t="n"/>
+      <c r="AT46" s="42" t="n"/>
+      <c r="AU46" s="43">
+        <f>IF(((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AV46" s="43">
+        <f>IF(((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AW46" s="43">
+        <f>IF(((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
+        <v/>
+      </c>
+      <c r="AX46" s="44" t="n"/>
+      <c r="AY46" s="44" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Marina → Abu Dhabi Corniche</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="32" t="n"/>
+      <c r="H47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="33">
+        <f>60*D47/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J47" s="33">
+        <f>I47+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K47" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J47,1))</f>
+        <v/>
+      </c>
+      <c r="L47" s="34">
+        <f>ROUND(365*mech_uptime*H47,0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N47" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O47" s="34">
+        <f>ROUND(K47*L47*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q47" s="36">
+        <f>pax_cap*P47</f>
+        <v/>
+      </c>
+      <c r="R47" s="34">
+        <f>Q47*O47</f>
+        <v/>
+      </c>
+      <c r="S47" s="37">
+        <f>E47*discount</f>
+        <v/>
+      </c>
+      <c r="T47" s="38">
+        <f>S47*R47</f>
+        <v/>
+      </c>
+      <c r="U47" s="38">
+        <f>(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V47" s="38">
+        <f>VLOOKUP(B47,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W47" s="38">
+        <f>VLOOKUP(B47,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X47" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y47" s="38">
+        <f>VLOOKUP(B47,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z47" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA47" s="38">
+        <f>U47+V47+W47+X47+Y47+Z47</f>
+        <v/>
+      </c>
+      <c r="AB47" s="38">
+        <f>VLOOKUP(B47,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC47" s="38">
+        <f>T47-AA47</f>
+        <v/>
+      </c>
+      <c r="AD47" s="35">
+        <f>IF(T47=0,"",AC47/T47)</f>
+        <v/>
+      </c>
+      <c r="AE47" s="36">
+        <f>IF(AC47&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/AC47)</f>
+        <v/>
+      </c>
+      <c r="AF47" s="33">
+        <f>((D47*O47/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D47*O47*VLOOKUP(B47,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG47" s="31" t="n"/>
+      <c r="AH47" s="32" t="n"/>
+      <c r="AI47" s="32" t="n"/>
+      <c r="AJ47" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK47" s="34">
+        <f>IF(AG47="","",AG47*AJ47)</f>
+        <v/>
+      </c>
+      <c r="AL47" s="34">
+        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AT47="",9.9E+99,AT47),FLOOR(AK47/R47,1)))</f>
+        <v/>
+      </c>
+      <c r="AM47" s="38">
+        <f>IF(AL47="","",AL47*T47)</f>
+        <v/>
+      </c>
+      <c r="AN47" s="36">
+        <f>IF(OR(AG47="",R47=0),"",MIN(IF(AT47="",9.9E+99,AT47),AK47/R47))</f>
+        <v/>
+      </c>
+      <c r="AO47" s="38">
+        <f>IF(AN47="","",AN47*T47)</f>
+        <v/>
+      </c>
+      <c r="AP47" s="40" t="n"/>
+      <c r="AQ47" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR47" s="41" t="n"/>
+      <c r="AS47" s="41" t="n"/>
+      <c r="AT47" s="42" t="n"/>
+      <c r="AU47" s="43">
+        <f>IF(((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_thin*ROUND(K47*L47*revleg_thin,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_thin,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AV47" s="43">
+        <f>IF(((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_mid*ROUND(K47*L47*revleg_mid,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_mid,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AW47" s="43">
+        <f>IF(((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47))&lt;=0,"",VLOOKUP(B47,country_opex,7,FALSE)/((S47*pax_cap*load_full*ROUND(K47*L47*revleg_full,0))-(((battery/range_nm)*D47*ROUND(K47*L47*revleg_full,0)*VLOOKUP(B47,country_opex,3,FALSE))+V47+W47+X47+Y47+Z47)))</f>
+        <v/>
+      </c>
+      <c r="AX47" s="44" t="n"/>
+      <c r="AY47" s="44" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Wynn Al Marjan Island arrival lagoon</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="n">
+        <v>56</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F48" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G48" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="33">
+        <f>60*D48/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J48" s="33">
+        <f>I48+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K48" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J48,1))</f>
+        <v/>
+      </c>
+      <c r="L48" s="34">
+        <f>ROUND(365*mech_uptime*H48,0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N48" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O48" s="34">
+        <f>ROUND(K48*L48*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P48" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q48" s="36">
+        <f>pax_cap*P48</f>
+        <v/>
+      </c>
+      <c r="R48" s="34">
+        <f>Q48*O48</f>
+        <v/>
+      </c>
+      <c r="S48" s="37">
+        <f>E48*discount</f>
+        <v/>
+      </c>
+      <c r="T48" s="38">
+        <f>S48*R48</f>
+        <v/>
+      </c>
+      <c r="U48" s="38">
+        <f>(battery/range_nm)*D48*O48*VLOOKUP(B48,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V48" s="38">
+        <f>VLOOKUP(B48,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W48" s="38">
+        <f>VLOOKUP(B48,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X48" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y48" s="38">
+        <f>VLOOKUP(B48,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z48" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA48" s="38">
+        <f>U48+V48+W48+X48+Y48+Z48</f>
+        <v/>
+      </c>
+      <c r="AB48" s="38">
+        <f>VLOOKUP(B48,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC48" s="38">
+        <f>T48-AA48</f>
+        <v/>
+      </c>
+      <c r="AD48" s="35">
+        <f>IF(T48=0,"",AC48/T48)</f>
+        <v/>
+      </c>
+      <c r="AE48" s="36">
+        <f>IF(AC48&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/AC48)</f>
+        <v/>
+      </c>
+      <c r="AF48" s="33">
+        <f>((D48*O48/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D48*O48*VLOOKUP(B48,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG48" s="31" t="n">
+        <v>60000</v>
+      </c>
+      <c r="AH48" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="AI48" s="32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AJ48" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK48" s="34">
+        <f>IF(AG48="","",AG48*AJ48)</f>
+        <v/>
+      </c>
+      <c r="AL48" s="34">
+        <f>IF(OR(AG48="",R48=0),"",MIN(IF(AT48="",9.9E+99,AT48),FLOOR(AK48/R48,1)))</f>
+        <v/>
+      </c>
+      <c r="AM48" s="38">
+        <f>IF(AL48="","",AL48*T48)</f>
+        <v/>
+      </c>
+      <c r="AN48" s="36">
+        <f>IF(OR(AG48="",R48=0),"",MIN(IF(AT48="",9.9E+99,AT48),AK48/R48))</f>
+        <v/>
+      </c>
+      <c r="AO48" s="38">
+        <f>IF(AN48="","",AN48*T48)</f>
+        <v/>
+      </c>
+      <c r="AP48" s="40" t="n"/>
+      <c r="AQ48" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR48" s="41" t="n"/>
+      <c r="AS48" s="41" t="n"/>
+      <c r="AT48" s="42" t="n"/>
+      <c r="AU48" s="43">
+        <f>IF(((S48*pax_cap*load_thin*ROUND(K48*L48*revleg_thin,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_thin,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_thin*ROUND(K48*L48*revleg_thin,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_thin,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
+        <v/>
+      </c>
+      <c r="AV48" s="43">
+        <f>IF(((S48*pax_cap*load_mid*ROUND(K48*L48*revleg_mid,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_mid,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_mid*ROUND(K48*L48*revleg_mid,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_mid,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
+        <v/>
+      </c>
+      <c r="AW48" s="43">
+        <f>IF(((S48*pax_cap*load_full*ROUND(K48*L48*revleg_full,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_full,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48))&lt;=0,"",VLOOKUP(B48,country_opex,7,FALSE)/((S48*pax_cap*load_full*ROUND(K48*L48*revleg_full,0))-(((battery/range_nm)*D48*ROUND(K48*L48*revleg_full,0)*VLOOKUP(B48,country_opex,3,FALSE))+V48+W48+X48+Y48+Z48)))</f>
+        <v/>
+      </c>
+      <c r="AX48" s="44" t="inlineStr">
+        <is>
+          <t>Wynn Al Marjan (first UAE gaming resort) opens early 2027: 1,217 rooms + 297 residences. No marine transfer today. T5/low - greenfield.</t>
+        </is>
+      </c>
+      <c r="AY48" s="44" t="inlineStr">
+        <is>
+          <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>Ushuaïa Dubai Harbour Experience → Marina Mall / Breakwater Marina</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="33">
+        <f>60*D49/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J49" s="33">
+        <f>I49+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K49" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J49,1))</f>
+        <v/>
+      </c>
+      <c r="L49" s="34">
+        <f>ROUND(365*mech_uptime*H49,0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N49" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O49" s="34">
+        <f>ROUND(K49*L49*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P49" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q49" s="36">
+        <f>pax_cap*P49</f>
+        <v/>
+      </c>
+      <c r="R49" s="34">
+        <f>Q49*O49</f>
+        <v/>
+      </c>
+      <c r="S49" s="37">
+        <f>E49*discount</f>
+        <v/>
+      </c>
+      <c r="T49" s="38">
+        <f>S49*R49</f>
+        <v/>
+      </c>
+      <c r="U49" s="38">
+        <f>(battery/range_nm)*D49*O49*VLOOKUP(B49,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V49" s="38">
+        <f>VLOOKUP(B49,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W49" s="38">
+        <f>VLOOKUP(B49,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X49" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y49" s="38">
+        <f>VLOOKUP(B49,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z49" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA49" s="38">
+        <f>U49+V49+W49+X49+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB49" s="38">
+        <f>VLOOKUP(B49,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC49" s="38">
+        <f>T49-AA49</f>
+        <v/>
+      </c>
+      <c r="AD49" s="35">
+        <f>IF(T49=0,"",AC49/T49)</f>
+        <v/>
+      </c>
+      <c r="AE49" s="36">
+        <f>IF(AC49&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/AC49)</f>
+        <v/>
+      </c>
+      <c r="AF49" s="33">
+        <f>((D49*O49/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D49*O49*VLOOKUP(B49,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG49" s="31" t="n"/>
+      <c r="AH49" s="32" t="n"/>
+      <c r="AI49" s="32" t="n"/>
+      <c r="AJ49" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK49" s="34">
+        <f>IF(AG49="","",AG49*AJ49)</f>
+        <v/>
+      </c>
+      <c r="AL49" s="34">
+        <f>IF(OR(AG49="",R49=0),"",MIN(IF(AT49="",9.9E+99,AT49),FLOOR(AK49/R49,1)))</f>
+        <v/>
+      </c>
+      <c r="AM49" s="38">
+        <f>IF(AL49="","",AL49*T49)</f>
+        <v/>
+      </c>
+      <c r="AN49" s="36">
+        <f>IF(OR(AG49="",R49=0),"",MIN(IF(AT49="",9.9E+99,AT49),AK49/R49))</f>
+        <v/>
+      </c>
+      <c r="AO49" s="38">
+        <f>IF(AN49="","",AN49*T49)</f>
+        <v/>
+      </c>
+      <c r="AP49" s="40" t="n"/>
+      <c r="AQ49" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR49" s="41" t="n"/>
+      <c r="AS49" s="41" t="n"/>
+      <c r="AT49" s="42" t="n"/>
+      <c r="AU49" s="43">
+        <f>IF(((S49*pax_cap*load_thin*ROUND(K49*L49*revleg_thin,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_thin,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_thin*ROUND(K49*L49*revleg_thin,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_thin,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
+        <v/>
+      </c>
+      <c r="AV49" s="43">
+        <f>IF(((S49*pax_cap*load_mid*ROUND(K49*L49*revleg_mid,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_mid,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_mid*ROUND(K49*L49*revleg_mid,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_mid,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
+        <v/>
+      </c>
+      <c r="AW49" s="43">
+        <f>IF(((S49*pax_cap*load_full*ROUND(K49*L49*revleg_full,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_full,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49))&lt;=0,"",VLOOKUP(B49,country_opex,7,FALSE)/((S49*pax_cap*load_full*ROUND(K49*L49*revleg_full,0))-(((battery/range_nm)*D49*ROUND(K49*L49*revleg_full,0)*VLOOKUP(B49,country_opex,3,FALSE))+V49+W49+X49+Y49+Z49)))</f>
+        <v/>
+      </c>
+      <c r="AX49" s="44" t="n"/>
+      <c r="AY49" s="44" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Marina Mall / Breakwater Marina</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E50" s="26" t="n">
+        <v>110</v>
+      </c>
+      <c r="F50" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="33">
+        <f>60*D50/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J50" s="33">
+        <f>I50+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K50" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J50,1))</f>
+        <v/>
+      </c>
+      <c r="L50" s="34">
+        <f>ROUND(365*mech_uptime*H50,0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N50" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O50" s="34">
+        <f>ROUND(K50*L50*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P50" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q50" s="36">
+        <f>pax_cap*P50</f>
+        <v/>
+      </c>
+      <c r="R50" s="34">
+        <f>Q50*O50</f>
+        <v/>
+      </c>
+      <c r="S50" s="37">
+        <f>E50*discount</f>
+        <v/>
+      </c>
+      <c r="T50" s="38">
+        <f>S50*R50</f>
+        <v/>
+      </c>
+      <c r="U50" s="38">
+        <f>(battery/range_nm)*D50*O50*VLOOKUP(B50,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V50" s="38">
+        <f>VLOOKUP(B50,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W50" s="38">
+        <f>VLOOKUP(B50,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X50" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y50" s="38">
+        <f>VLOOKUP(B50,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z50" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA50" s="38">
+        <f>U50+V50+W50+X50+Y50+Z50</f>
+        <v/>
+      </c>
+      <c r="AB50" s="38">
+        <f>VLOOKUP(B50,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC50" s="38">
+        <f>T50-AA50</f>
+        <v/>
+      </c>
+      <c r="AD50" s="35">
+        <f>IF(T50=0,"",AC50/T50)</f>
+        <v/>
+      </c>
+      <c r="AE50" s="36">
+        <f>IF(AC50&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/AC50)</f>
+        <v/>
+      </c>
+      <c r="AF50" s="33">
+        <f>((D50*O50/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D50*O50*VLOOKUP(B50,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG50" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AH50" s="32" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="AI50" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AJ50" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK50" s="34">
+        <f>IF(AG50="","",AG50*AJ50)</f>
+        <v/>
+      </c>
+      <c r="AL50" s="34">
+        <f>IF(OR(AG50="",R50=0),"",MIN(IF(AT50="",9.9E+99,AT50),FLOOR(AK50/R50,1)))</f>
+        <v/>
+      </c>
+      <c r="AM50" s="38">
+        <f>IF(AL50="","",AL50*T50)</f>
+        <v/>
+      </c>
+      <c r="AN50" s="36">
+        <f>IF(OR(AG50="",R50=0),"",MIN(IF(AT50="",9.9E+99,AT50),AK50/R50))</f>
+        <v/>
+      </c>
+      <c r="AO50" s="38">
+        <f>IF(AN50="","",AN50*T50)</f>
+        <v/>
+      </c>
+      <c r="AP50" s="40" t="n"/>
+      <c r="AQ50" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR50" s="41" t="n"/>
+      <c r="AS50" s="41" t="n"/>
+      <c r="AT50" s="42" t="n"/>
+      <c r="AU50" s="43">
+        <f>IF(((S50*pax_cap*load_thin*ROUND(K50*L50*revleg_thin,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_thin,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_thin*ROUND(K50*L50*revleg_thin,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_thin,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
+        <v/>
+      </c>
+      <c r="AV50" s="43">
+        <f>IF(((S50*pax_cap*load_mid*ROUND(K50*L50*revleg_mid,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_mid,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_mid*ROUND(K50*L50*revleg_mid,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_mid,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
+        <v/>
+      </c>
+      <c r="AW50" s="43">
+        <f>IF(((S50*pax_cap*load_full*ROUND(K50*L50*revleg_full,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_full,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50))&lt;=0,"",VLOOKUP(B50,country_opex,7,FALSE)/((S50*pax_cap*load_full*ROUND(K50*L50*revleg_full,0))-(((battery/range_nm)*D50*ROUND(K50*L50*revleg_full,0)*VLOOKUP(B50,country_opex,3,FALSE))+V50+W50+X50+Y50+Z50)))</f>
+        <v/>
+      </c>
+      <c r="AX50" s="44" t="inlineStr">
         <is>
           <t>No Dubai&lt;-&gt;AD ferry. Whole-yacht charter AED 4,500/hr (8-pax ~$95-150/seat); limo AED 250-350. T5/low - opportunity-to-create.</t>
         </is>
       </c>
-      <c r="AX39" s="44" t="inlineStr">
+      <c r="AY50" s="44" t="inlineStr">
         <is>
           <t>UAE-DEMAND-ANCHORS-2026-06-17.json — sourcing wave: RTA Marine 18M riders 2024; DET 43M room-nights; DCT AD 4.8M hotel visitors; RAKTDA 4.35M guest-nights; Miral Yas 38M visits; Marjan/Skift Wynn projections; SCTDA Sharjah 1.6M.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="45" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>UAE (Careem)</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>Dubai Harbour Marina → Marina Mall / Breakwater Marina</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
+      <c r="H51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="33">
+        <f>60*D51/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J51" s="33">
+        <f>I51+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K51" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J51,1))</f>
+        <v/>
+      </c>
+      <c r="L51" s="34">
+        <f>ROUND(365*mech_uptime*H51,0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N51" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O51" s="34">
+        <f>ROUND(K51*L51*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P51" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q51" s="36">
+        <f>pax_cap*P51</f>
+        <v/>
+      </c>
+      <c r="R51" s="34">
+        <f>Q51*O51</f>
+        <v/>
+      </c>
+      <c r="S51" s="37">
+        <f>E51*discount</f>
+        <v/>
+      </c>
+      <c r="T51" s="38">
+        <f>S51*R51</f>
+        <v/>
+      </c>
+      <c r="U51" s="38">
+        <f>(battery/range_nm)*D51*O51*VLOOKUP(B51,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V51" s="38">
+        <f>VLOOKUP(B51,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W51" s="38">
+        <f>VLOOKUP(B51,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X51" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y51" s="38">
+        <f>VLOOKUP(B51,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z51" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA51" s="38">
+        <f>U51+V51+W51+X51+Y51+Z51</f>
+        <v/>
+      </c>
+      <c r="AB51" s="38">
+        <f>VLOOKUP(B51,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC51" s="38">
+        <f>T51-AA51</f>
+        <v/>
+      </c>
+      <c r="AD51" s="35">
+        <f>IF(T51=0,"",AC51/T51)</f>
+        <v/>
+      </c>
+      <c r="AE51" s="36">
+        <f>IF(AC51&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/AC51)</f>
+        <v/>
+      </c>
+      <c r="AF51" s="33">
+        <f>((D51*O51/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D51*O51*VLOOKUP(B51,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG51" s="31" t="n"/>
+      <c r="AH51" s="32" t="n"/>
+      <c r="AI51" s="32" t="n"/>
+      <c r="AJ51" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK51" s="34">
+        <f>IF(AG51="","",AG51*AJ51)</f>
+        <v/>
+      </c>
+      <c r="AL51" s="34">
+        <f>IF(OR(AG51="",R51=0),"",MIN(IF(AT51="",9.9E+99,AT51),FLOOR(AK51/R51,1)))</f>
+        <v/>
+      </c>
+      <c r="AM51" s="38">
+        <f>IF(AL51="","",AL51*T51)</f>
+        <v/>
+      </c>
+      <c r="AN51" s="36">
+        <f>IF(OR(AG51="",R51=0),"",MIN(IF(AT51="",9.9E+99,AT51),AK51/R51))</f>
+        <v/>
+      </c>
+      <c r="AO51" s="38">
+        <f>IF(AN51="","",AN51*T51)</f>
+        <v/>
+      </c>
+      <c r="AP51" s="40" t="n"/>
+      <c r="AQ51" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR51" s="41" t="n"/>
+      <c r="AS51" s="41" t="n"/>
+      <c r="AT51" s="42" t="n"/>
+      <c r="AU51" s="43">
+        <f>IF(((S51*pax_cap*load_thin*ROUND(K51*L51*revleg_thin,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_thin,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_thin*ROUND(K51*L51*revleg_thin,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_thin,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
+        <v/>
+      </c>
+      <c r="AV51" s="43">
+        <f>IF(((S51*pax_cap*load_mid*ROUND(K51*L51*revleg_mid,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_mid,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_mid*ROUND(K51*L51*revleg_mid,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_mid,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
+        <v/>
+      </c>
+      <c r="AW51" s="43">
+        <f>IF(((S51*pax_cap*load_full*ROUND(K51*L51*revleg_full,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_full,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51))&lt;=0,"",VLOOKUP(B51,country_opex,7,FALSE)/((S51*pax_cap*load_full*ROUND(K51*L51*revleg_full,0))-(((battery/range_nm)*D51*ROUND(K51*L51*revleg_full,0)*VLOOKUP(B51,country_opex,3,FALSE))+V51+W51+X51+Y51+Z51)))</f>
+        <v/>
+      </c>
+      <c r="AX51" s="44" t="n"/>
+      <c r="AY51" s="44" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="T40" s="46">
-        <f>SUM(T4:T39)</f>
-        <v/>
-      </c>
-      <c r="AC40" s="46">
-        <f>SUM(AC4:AC39)</f>
-        <v/>
-      </c>
-      <c r="AD40" s="47">
-        <f>IF(T40=0,"",AC40/T40)</f>
-        <v/>
-      </c>
-      <c r="AL40" s="48">
-        <f>SUM(AL4:AL39)</f>
-        <v/>
-      </c>
-      <c r="AM40" s="46">
-        <f>SUM(AM4:AM39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="T52" s="46">
+        <f>SUM(T4:T51)</f>
+        <v/>
+      </c>
+      <c r="AC52" s="46">
+        <f>SUM(AC4:AC51)</f>
+        <v/>
+      </c>
+      <c r="AD52" s="47">
+        <f>IF(T52=0,"",AC52/T52)</f>
+        <v/>
+      </c>
+      <c r="AL52" s="48">
+        <f>SUM(AL4:AL51)</f>
+        <v/>
+      </c>
+      <c r="AM52" s="46">
+        <f>SUM(AM4:AM51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B55" s="24" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C55" s="24" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E55" s="24" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>UAE (Careem)</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>network_sum / ceil</t>
         </is>
       </c>
-      <c r="C44" s="23">
-        <f>SUMIFS(AN4:AN39,A4:A39,"UAE (Careem)",AP4:AP39,"=",AQ4:AQ39,"=",AR4:AR39,"=")</f>
-        <v/>
-      </c>
-      <c r="D44" s="49">
-        <f>IF(C44=0,0,CEILING(C44,1))</f>
-        <v/>
-      </c>
-      <c r="E44" s="50">
-        <f>SUMIFS(AO4:AO39,A4:A39,"UAE (Careem)",AP4:AP39,"=",AQ4:AQ39,"=",AR4:AR39,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="45" t="inlineStr">
+      <c r="C56" s="23">
+        <f>SUMIFS(AN4:AN51,A4:A51,"UAE (Careem)",AP4:AP51,"=",AQ4:AQ51,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D56" s="49">
+        <f>IF(C56=0,0,CEILING(C56,1))</f>
+        <v/>
+      </c>
+      <c r="E56" s="50">
+        <f>SUMIFS(AO4:AO51,A4:A51,"UAE (Careem)",AP4:AP51,"=",AQ4:AQ51,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="45" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D45" s="48">
-        <f>SUM(D44:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="46">
-        <f>SUM(E44:E44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="51" t="inlineStr">
+      <c r="D57" s="48">
+        <f>SUM(D56:D56)</f>
+        <v/>
+      </c>
+      <c r="E57" s="46">
+        <f>SUM(E56:E56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D58" s="51">
+        <f>SUMIF(AQ4:AQ51,"Estimated",AL4:AL51)</f>
+        <v/>
+      </c>
+      <c r="E58" s="52">
+        <f>SUMIF(AQ4:AQ51,"Estimated",AM4:AM51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C47" s="52" t="inlineStr">
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>Abu Dhabi → Muscat (360.9nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>Fujairah → Muscat (149.1nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="54" t="inlineStr">
         <is>
           <t>Marina Mall / Breakwater Marina → Sir Bani Yas Cruise Port (93.1nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="52" t="inlineStr">
-        <is>
-          <t>Dubai Harbour Marina → Old Doha Port (195.42nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="52" t="inlineStr">
-        <is>
-          <t>Marina Mall / Breakwater Marina → Bahrain Financial Harbour Marina (235.44nm)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A42:L42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9465,7 +11724,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
@@ -9654,12 +11913,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="A26" s="55" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
